--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118597392</v>
+        <v>118596922</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588372</v>
+        <v>588264</v>
       </c>
       <c r="R8" t="n">
-        <v>6436011</v>
+        <v>6436046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118596922</v>
+        <v>118597392</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588264</v>
+        <v>588372</v>
       </c>
       <c r="R9" t="n">
-        <v>6436046</v>
+        <v>6436011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118597504</v>
+        <v>118597239</v>
       </c>
       <c r="B42" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5174,38 +5174,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5213,10 +5210,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588334</v>
+        <v>588323</v>
       </c>
       <c r="R42" t="n">
-        <v>6436022</v>
+        <v>6436028</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5276,7 +5273,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118597239</v>
+        <v>118594763</v>
       </c>
       <c r="B43" t="n">
         <v>97846</v>
@@ -5324,10 +5321,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588323</v>
+        <v>588231</v>
       </c>
       <c r="R43" t="n">
-        <v>6436028</v>
+        <v>6435990</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5387,10 +5384,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118594763</v>
+        <v>118597598</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5399,25 +5396,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5426,7 +5423,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5435,10 +5436,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588231</v>
+        <v>588224</v>
       </c>
       <c r="R44" t="n">
-        <v>6435990</v>
+        <v>6435937</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5498,10 +5499,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118597598</v>
+        <v>118597504</v>
       </c>
       <c r="B45" t="n">
-        <v>104940</v>
+        <v>90908</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5514,35 +5515,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588224</v>
+        <v>588334</v>
       </c>
       <c r="R45" t="n">
-        <v>6435937</v>
+        <v>6436022</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118594896</v>
+        <v>118597378</v>
       </c>
       <c r="B50" t="n">
         <v>104940</v>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>588223</v>
+        <v>588349</v>
       </c>
       <c r="R50" t="n">
-        <v>6435976</v>
+        <v>6436020</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118597378</v>
+        <v>118594896</v>
       </c>
       <c r="B51" t="n">
         <v>104940</v>
@@ -6216,10 +6216,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588349</v>
+        <v>588223</v>
       </c>
       <c r="R51" t="n">
-        <v>6436020</v>
+        <v>6435976</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -8176,10 +8176,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118660053</v>
+        <v>118660036</v>
       </c>
       <c r="B69" t="n">
-        <v>91823</v>
+        <v>97846</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8188,38 +8188,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8227,10 +8228,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588406</v>
+        <v>588380</v>
       </c>
       <c r="R69" t="n">
-        <v>6435986</v>
+        <v>6435970</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8290,10 +8291,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118660036</v>
+        <v>118660053</v>
       </c>
       <c r="B70" t="n">
-        <v>97846</v>
+        <v>91823</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8302,39 +8303,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588380</v>
+        <v>588406</v>
       </c>
       <c r="R70" t="n">
-        <v>6435970</v>
+        <v>6435986</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8744,10 +8744,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118659823</v>
+        <v>118596680</v>
       </c>
       <c r="B74" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8760,31 +8760,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8792,10 +8795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>588322</v>
+        <v>588251</v>
       </c>
       <c r="R74" t="n">
-        <v>6435984</v>
+        <v>6436043</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8822,12 +8825,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8855,10 +8858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118596680</v>
+        <v>118659823</v>
       </c>
       <c r="B75" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8871,34 +8874,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8906,10 +8906,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>588251</v>
+        <v>588322</v>
       </c>
       <c r="R75" t="n">
-        <v>6436043</v>
+        <v>6435984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -5162,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118597239</v>
+        <v>118597504</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5174,35 +5174,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5210,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588323</v>
+        <v>588334</v>
       </c>
       <c r="R42" t="n">
-        <v>6436028</v>
+        <v>6436022</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5273,7 +5276,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118594763</v>
+        <v>118597239</v>
       </c>
       <c r="B43" t="n">
         <v>97846</v>
@@ -5321,10 +5324,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588231</v>
+        <v>588323</v>
       </c>
       <c r="R43" t="n">
-        <v>6435990</v>
+        <v>6436028</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5384,10 +5387,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118597598</v>
+        <v>118594763</v>
       </c>
       <c r="B44" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5396,25 +5399,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,11 +5426,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5436,10 +5435,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588224</v>
+        <v>588231</v>
       </c>
       <c r="R44" t="n">
-        <v>6435937</v>
+        <v>6435990</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5499,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118597504</v>
+        <v>118597598</v>
       </c>
       <c r="B45" t="n">
-        <v>90908</v>
+        <v>104940</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5515,34 +5514,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588334</v>
+        <v>588224</v>
       </c>
       <c r="R45" t="n">
-        <v>6436022</v>
+        <v>6435937</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118597378</v>
+        <v>118594896</v>
       </c>
       <c r="B50" t="n">
         <v>104940</v>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>588349</v>
+        <v>588223</v>
       </c>
       <c r="R50" t="n">
-        <v>6436020</v>
+        <v>6435976</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118594896</v>
+        <v>118597378</v>
       </c>
       <c r="B51" t="n">
         <v>104940</v>
@@ -6216,10 +6216,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588223</v>
+        <v>588349</v>
       </c>
       <c r="R51" t="n">
-        <v>6435976</v>
+        <v>6436020</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118597484</v>
+        <v>118596776</v>
       </c>
       <c r="B2" t="n">
         <v>104940</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588339</v>
+        <v>588272</v>
       </c>
       <c r="R2" t="n">
-        <v>6436034</v>
+        <v>6436033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118597100</v>
+        <v>118597219</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -825,7 +825,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588307</v>
+        <v>588317</v>
       </c>
       <c r="R3" t="n">
-        <v>6436069</v>
+        <v>6436035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118597343</v>
+        <v>118597187</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -945,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588368</v>
+        <v>588288</v>
       </c>
       <c r="R4" t="n">
-        <v>6436025</v>
+        <v>6436050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118597015</v>
+        <v>118597451</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588316</v>
+        <v>588350</v>
       </c>
       <c r="R5" t="n">
-        <v>6436073</v>
+        <v>6436007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118597267</v>
+        <v>118597484</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588348</v>
+        <v>588339</v>
       </c>
       <c r="R6" t="n">
-        <v>6436039</v>
+        <v>6436034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118596651</v>
+        <v>118594699</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1278,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588258</v>
+        <v>588208</v>
       </c>
       <c r="R7" t="n">
-        <v>6435987</v>
+        <v>6435965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118596922</v>
+        <v>118594991</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1380,7 +1384,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588264</v>
+        <v>588220</v>
       </c>
       <c r="R8" t="n">
-        <v>6436046</v>
+        <v>6435964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118597392</v>
+        <v>118596948</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1500,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588372</v>
+        <v>588269</v>
       </c>
       <c r="R9" t="n">
-        <v>6436011</v>
+        <v>6436070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118597539</v>
+        <v>118597164</v>
       </c>
       <c r="B11" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1698,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588236</v>
+        <v>588296</v>
       </c>
       <c r="R11" t="n">
-        <v>6436001</v>
+        <v>6436035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118594991</v>
+        <v>118594819</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1828,11 +1836,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1841,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588220</v>
+        <v>588240</v>
       </c>
       <c r="R12" t="n">
-        <v>6435964</v>
+        <v>6435993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118596948</v>
+        <v>118597574</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1952,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588269</v>
+        <v>588227</v>
       </c>
       <c r="R13" t="n">
-        <v>6436070</v>
+        <v>6435928</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118594446</v>
+        <v>118594955</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2054,11 +2058,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588224</v>
+        <v>588225</v>
       </c>
       <c r="R14" t="n">
-        <v>6435907</v>
+        <v>6435968</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118596776</v>
+        <v>118594896</v>
       </c>
       <c r="B15" t="n">
         <v>104940</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588272</v>
+        <v>588223</v>
       </c>
       <c r="R15" t="n">
-        <v>6436033</v>
+        <v>6435976</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118597561</v>
+        <v>118597118</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2280,11 +2280,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2293,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588237</v>
+        <v>588306</v>
       </c>
       <c r="R16" t="n">
-        <v>6435907</v>
+        <v>6436055</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118594834</v>
+        <v>118597065</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,35 +2364,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2404,13 +2400,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588243</v>
+        <v>588304</v>
       </c>
       <c r="R17" t="n">
-        <v>6435983</v>
+        <v>6436063</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,13 +2438,17 @@
           <t>2024-07-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118594511</v>
+        <v>118597293</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,50 +2479,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27374, Långgölen, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588220</v>
+        <v>588360</v>
       </c>
       <c r="R18" t="n">
-        <v>6435969</v>
+        <v>6436048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,7 +2581,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118594734</v>
+        <v>118597239</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2626,14 +2625,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588223</v>
+        <v>588323</v>
       </c>
       <c r="R19" t="n">
-        <v>6435976</v>
+        <v>6436028</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2692,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118597451</v>
+        <v>118597267</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2741,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588350</v>
+        <v>588348</v>
       </c>
       <c r="R20" t="n">
-        <v>6436007</v>
+        <v>6436039</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118597410</v>
+        <v>118594936</v>
       </c>
       <c r="B21" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,30 +2815,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2848,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588363</v>
+        <v>588234</v>
       </c>
       <c r="R21" t="n">
-        <v>6436008</v>
+        <v>6435965</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,7 +2918,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118594849</v>
+        <v>118594683</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -2959,14 +2966,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588235</v>
+        <v>588206</v>
       </c>
       <c r="R22" t="n">
-        <v>6435981</v>
+        <v>6435960</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3033,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118597118</v>
+        <v>118597458</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -3074,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588306</v>
+        <v>588342</v>
       </c>
       <c r="R23" t="n">
-        <v>6436055</v>
+        <v>6436015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3137,7 +3144,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118597187</v>
+        <v>118594834</v>
       </c>
       <c r="B24" t="n">
         <v>97846</v>
@@ -3185,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588288</v>
+        <v>588243</v>
       </c>
       <c r="R24" t="n">
-        <v>6436050</v>
+        <v>6435983</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3248,7 +3255,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118597432</v>
+        <v>118594734</v>
       </c>
       <c r="B25" t="n">
         <v>97846</v>
@@ -3292,14 +3299,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588370</v>
+        <v>588223</v>
       </c>
       <c r="R25" t="n">
-        <v>6436006</v>
+        <v>6435976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3359,7 +3366,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118596857</v>
+        <v>118595018</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3398,23 +3405,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A  27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588255</v>
+        <v>588242</v>
       </c>
       <c r="R26" t="n">
-        <v>6436028</v>
+        <v>6435991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3474,7 +3477,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118594936</v>
+        <v>118594488</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3508,11 +3511,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -3526,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588234</v>
+        <v>588214</v>
       </c>
       <c r="R27" t="n">
-        <v>6435965</v>
+        <v>6435937</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,10 +3588,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118594721</v>
+        <v>118597378</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3601,25 +3600,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3628,11 +3627,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588225</v>
+        <v>588349</v>
       </c>
       <c r="R28" t="n">
-        <v>6435977</v>
+        <v>6436020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,7 +3699,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118597219</v>
+        <v>118594849</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3756,10 +3751,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588317</v>
+        <v>588235</v>
       </c>
       <c r="R29" t="n">
-        <v>6436035</v>
+        <v>6435981</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3819,7 +3814,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118596899</v>
+        <v>118596651</v>
       </c>
       <c r="B30" t="n">
         <v>97846</v>
@@ -3853,12 +3848,12 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3867,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588276</v>
+        <v>588258</v>
       </c>
       <c r="R30" t="n">
-        <v>6436025</v>
+        <v>6435987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3930,7 +3925,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118594699</v>
+        <v>118597432</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3978,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588208</v>
+        <v>588370</v>
       </c>
       <c r="R31" t="n">
-        <v>6435965</v>
+        <v>6436006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4041,10 +4036,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118596804</v>
+        <v>118597504</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4053,39 +4048,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4093,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588239</v>
+        <v>588334</v>
       </c>
       <c r="R32" t="n">
-        <v>6436018</v>
+        <v>6436022</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,10 +4150,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118597524</v>
+        <v>118597136</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,35 +4162,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4204,10 +4201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588256</v>
+        <v>588295</v>
       </c>
       <c r="R33" t="n">
-        <v>6436024</v>
+        <v>6436061</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4267,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118594955</v>
+        <v>118597539</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4279,25 +4276,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4315,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588225</v>
+        <v>588236</v>
       </c>
       <c r="R34" t="n">
-        <v>6435968</v>
+        <v>6436001</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4378,7 +4375,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118597164</v>
+        <v>118597524</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4426,10 +4423,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588296</v>
+        <v>588256</v>
       </c>
       <c r="R35" t="n">
-        <v>6436035</v>
+        <v>6436024</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,7 +4486,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118597574</v>
+        <v>118594763</v>
       </c>
       <c r="B36" t="n">
         <v>97846</v>
@@ -4537,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588227</v>
+        <v>588231</v>
       </c>
       <c r="R36" t="n">
-        <v>6435928</v>
+        <v>6435990</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4600,7 +4597,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118594683</v>
+        <v>118596922</v>
       </c>
       <c r="B37" t="n">
         <v>97846</v>
@@ -4639,23 +4636,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588206</v>
+        <v>588264</v>
       </c>
       <c r="R37" t="n">
-        <v>6435960</v>
+        <v>6436046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4715,10 +4708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118597136</v>
+        <v>118597100</v>
       </c>
       <c r="B38" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4727,38 +4720,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4766,10 +4756,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588295</v>
+        <v>588307</v>
       </c>
       <c r="R38" t="n">
-        <v>6436061</v>
+        <v>6436069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4829,7 +4819,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118594819</v>
+        <v>118597252</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4877,10 +4867,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588240</v>
+        <v>588324</v>
       </c>
       <c r="R39" t="n">
-        <v>6435993</v>
+        <v>6436038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4940,7 +4930,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118597469</v>
+        <v>118597561</v>
       </c>
       <c r="B40" t="n">
         <v>97846</v>
@@ -4979,7 +4969,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4988,10 +4982,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588317</v>
+        <v>588237</v>
       </c>
       <c r="R40" t="n">
-        <v>6435988</v>
+        <v>6435907</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5051,7 +5045,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118594488</v>
+        <v>118596804</v>
       </c>
       <c r="B41" t="n">
         <v>97846</v>
@@ -5085,7 +5079,11 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5099,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588214</v>
+        <v>588239</v>
       </c>
       <c r="R41" t="n">
-        <v>6435937</v>
+        <v>6436018</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,10 +5160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118597504</v>
+        <v>118596857</v>
       </c>
       <c r="B42" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5174,49 +5172,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A  27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588334</v>
+        <v>588255</v>
       </c>
       <c r="R42" t="n">
-        <v>6436022</v>
+        <v>6436028</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5276,7 +5275,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118597239</v>
+        <v>118594511</v>
       </c>
       <c r="B43" t="n">
         <v>97846</v>
@@ -5315,19 +5314,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374, Långgölen, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588323</v>
+        <v>588220</v>
       </c>
       <c r="R43" t="n">
-        <v>6436028</v>
+        <v>6435969</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118594763</v>
+        <v>118594446</v>
       </c>
       <c r="B44" t="n">
         <v>97846</v>
@@ -5426,7 +5429,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5435,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588231</v>
+        <v>588224</v>
       </c>
       <c r="R44" t="n">
-        <v>6435990</v>
+        <v>6435907</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5498,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118597598</v>
+        <v>118594721</v>
       </c>
       <c r="B45" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5510,25 +5517,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5539,7 +5546,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5550,10 +5557,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588224</v>
+        <v>588225</v>
       </c>
       <c r="R45" t="n">
-        <v>6435937</v>
+        <v>6435977</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5613,7 +5620,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118594459</v>
+        <v>118597392</v>
       </c>
       <c r="B46" t="n">
         <v>97846</v>
@@ -5661,10 +5668,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>588238</v>
+        <v>588372</v>
       </c>
       <c r="R46" t="n">
-        <v>6435934</v>
+        <v>6436011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5724,7 +5731,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118597252</v>
+        <v>118597015</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5772,10 +5779,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588324</v>
+        <v>588316</v>
       </c>
       <c r="R47" t="n">
-        <v>6436038</v>
+        <v>6436073</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6057,10 +6064,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118594896</v>
+        <v>118597469</v>
       </c>
       <c r="B50" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6069,25 +6076,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6105,10 +6112,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>588223</v>
+        <v>588317</v>
       </c>
       <c r="R50" t="n">
-        <v>6435976</v>
+        <v>6435988</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6168,10 +6175,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118597378</v>
+        <v>118594459</v>
       </c>
       <c r="B51" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6180,25 +6187,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6216,10 +6223,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588349</v>
+        <v>588238</v>
       </c>
       <c r="R51" t="n">
-        <v>6436020</v>
+        <v>6435934</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6279,7 +6286,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118597458</v>
+        <v>118596899</v>
       </c>
       <c r="B52" t="n">
         <v>97846</v>
@@ -6313,12 +6320,12 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6327,10 +6334,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>588342</v>
+        <v>588276</v>
       </c>
       <c r="R52" t="n">
-        <v>6436015</v>
+        <v>6436025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6390,10 +6397,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118597293</v>
+        <v>118597410</v>
       </c>
       <c r="B53" t="n">
-        <v>90908</v>
+        <v>94620</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6406,34 +6413,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>588360</v>
+        <v>588363</v>
       </c>
       <c r="R53" t="n">
-        <v>6436048</v>
+        <v>6436008</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118594857</v>
+        <v>118597343</v>
       </c>
       <c r="B54" t="n">
         <v>97846</v>
@@ -6552,10 +6552,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588230</v>
+        <v>588368</v>
       </c>
       <c r="R54" t="n">
-        <v>6435980</v>
+        <v>6436025</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118595018</v>
+        <v>118594857</v>
       </c>
       <c r="B55" t="n">
         <v>97846</v>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588242</v>
+        <v>588230</v>
       </c>
       <c r="R55" t="n">
-        <v>6435991</v>
+        <v>6435980</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118597065</v>
+        <v>118597598</v>
       </c>
       <c r="B57" t="n">
-        <v>57306</v>
+        <v>104940</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6849,35 +6849,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6885,13 +6889,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>588304</v>
+        <v>588224</v>
       </c>
       <c r="R57" t="n">
-        <v>6436063</v>
+        <v>6435937</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6923,17 +6927,13 @@
           <t>2024-07-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118659809</v>
+        <v>118659974</v>
       </c>
       <c r="B58" t="n">
         <v>97846</v>
@@ -7000,10 +7000,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>588355</v>
+        <v>588387</v>
       </c>
       <c r="R58" t="n">
-        <v>6436008</v>
+        <v>6435972</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118596742</v>
+        <v>118659907</v>
       </c>
       <c r="B59" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7079,34 +7079,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7114,10 +7111,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>588295</v>
+        <v>588400</v>
       </c>
       <c r="R59" t="n">
-        <v>6436033</v>
+        <v>6435993</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7144,12 +7141,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7177,7 +7174,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118659989</v>
+        <v>118659945</v>
       </c>
       <c r="B60" t="n">
         <v>97846</v>
@@ -7225,10 +7222,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588391</v>
+        <v>588429</v>
       </c>
       <c r="R60" t="n">
-        <v>6435977</v>
+        <v>6435973</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7288,10 +7285,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118660013</v>
+        <v>118659872</v>
       </c>
       <c r="B61" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7300,25 +7297,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7336,10 +7333,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>588383</v>
+        <v>588386</v>
       </c>
       <c r="R61" t="n">
-        <v>6435986</v>
+        <v>6436004</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,10 +7396,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118659848</v>
+        <v>118596680</v>
       </c>
       <c r="B62" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7415,31 +7412,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>588419</v>
+        <v>588251</v>
       </c>
       <c r="R62" t="n">
-        <v>6435987</v>
+        <v>6436043</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7510,10 +7510,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118659974</v>
+        <v>118659964</v>
       </c>
       <c r="B63" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7522,33 +7522,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7558,10 +7554,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>588387</v>
+        <v>588411</v>
       </c>
       <c r="R63" t="n">
-        <v>6435972</v>
+        <v>6435983</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7621,10 +7617,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118659964</v>
+        <v>118660053</v>
       </c>
       <c r="B64" t="n">
-        <v>94620</v>
+        <v>91823</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7633,31 +7629,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7665,10 +7668,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588411</v>
+        <v>588406</v>
       </c>
       <c r="R64" t="n">
-        <v>6435983</v>
+        <v>6435986</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7728,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118659892</v>
+        <v>118596728</v>
       </c>
       <c r="B65" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7744,31 +7747,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7776,10 +7782,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588413</v>
+        <v>588287</v>
       </c>
       <c r="R65" t="n">
-        <v>6435984</v>
+        <v>6436027</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7806,12 +7812,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7839,10 +7845,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118660618</v>
+        <v>118596709</v>
       </c>
       <c r="B66" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7855,35 +7861,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7891,10 +7896,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>588407</v>
+        <v>588280</v>
       </c>
       <c r="R66" t="n">
-        <v>6435952</v>
+        <v>6436028</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7921,12 +7926,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7954,7 +7959,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118659907</v>
+        <v>118660036</v>
       </c>
       <c r="B67" t="n">
         <v>97846</v>
@@ -7993,7 +7998,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -8002,10 +8011,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>588400</v>
+        <v>588380</v>
       </c>
       <c r="R67" t="n">
-        <v>6435993</v>
+        <v>6435970</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8065,7 +8074,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118659916</v>
+        <v>118659823</v>
       </c>
       <c r="B68" t="n">
         <v>97846</v>
@@ -8113,10 +8122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>588419</v>
+        <v>588322</v>
       </c>
       <c r="R68" t="n">
-        <v>6435978</v>
+        <v>6435984</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8176,7 +8185,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118660036</v>
+        <v>118660013</v>
       </c>
       <c r="B69" t="n">
         <v>97846</v>
@@ -8215,11 +8224,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588380</v>
+        <v>588383</v>
       </c>
       <c r="R69" t="n">
-        <v>6435970</v>
+        <v>6435986</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8291,10 +8296,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118660053</v>
+        <v>118659809</v>
       </c>
       <c r="B70" t="n">
-        <v>91823</v>
+        <v>97846</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8303,38 +8308,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8342,10 +8344,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588406</v>
+        <v>588355</v>
       </c>
       <c r="R70" t="n">
-        <v>6435986</v>
+        <v>6436008</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8405,10 +8407,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118659872</v>
+        <v>118659790</v>
       </c>
       <c r="B71" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8417,25 +8419,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8453,10 +8455,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588386</v>
+        <v>588326</v>
       </c>
       <c r="R71" t="n">
-        <v>6436004</v>
+        <v>6436033</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8516,10 +8518,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118596728</v>
+        <v>118660648</v>
       </c>
       <c r="B72" t="n">
-        <v>89999</v>
+        <v>91779</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8528,32 +8530,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2051</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8567,10 +8565,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>588287</v>
+        <v>588400</v>
       </c>
       <c r="R72" t="n">
-        <v>6436027</v>
+        <v>6435972</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8597,12 +8595,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8630,10 +8628,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118596695</v>
+        <v>118659848</v>
       </c>
       <c r="B73" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8646,34 +8644,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8681,10 +8676,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>588270</v>
+        <v>588419</v>
       </c>
       <c r="R73" t="n">
-        <v>6436044</v>
+        <v>6435987</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8711,12 +8706,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8744,7 +8739,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118596680</v>
+        <v>118596695</v>
       </c>
       <c r="B74" t="n">
         <v>89999</v>
@@ -8779,7 +8774,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8795,10 +8790,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>588251</v>
+        <v>588270</v>
       </c>
       <c r="R74" t="n">
-        <v>6436043</v>
+        <v>6436044</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8858,7 +8853,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118659823</v>
+        <v>118659989</v>
       </c>
       <c r="B75" t="n">
         <v>97846</v>
@@ -8906,10 +8901,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>588322</v>
+        <v>588391</v>
       </c>
       <c r="R75" t="n">
-        <v>6435984</v>
+        <v>6435977</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8969,7 +8964,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118659790</v>
+        <v>118659892</v>
       </c>
       <c r="B76" t="n">
         <v>97846</v>
@@ -9017,10 +9012,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>588326</v>
+        <v>588413</v>
       </c>
       <c r="R76" t="n">
-        <v>6436033</v>
+        <v>6435984</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9080,10 +9075,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118660648</v>
+        <v>118659916</v>
       </c>
       <c r="B77" t="n">
-        <v>91779</v>
+        <v>97846</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9092,34 +9087,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9127,10 +9123,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>588400</v>
+        <v>588419</v>
       </c>
       <c r="R77" t="n">
-        <v>6435972</v>
+        <v>6435978</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9190,10 +9186,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118596709</v>
+        <v>118660618</v>
       </c>
       <c r="B78" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9206,34 +9202,35 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9241,10 +9238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588280</v>
+        <v>588407</v>
       </c>
       <c r="R78" t="n">
-        <v>6436028</v>
+        <v>6435952</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9271,12 +9268,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9304,10 +9301,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118659945</v>
+        <v>118596742</v>
       </c>
       <c r="B79" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9320,31 +9317,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>588429</v>
+        <v>588295</v>
       </c>
       <c r="R79" t="n">
-        <v>6435973</v>
+        <v>6436033</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118594819</v>
+        <v>118594955</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588240</v>
+        <v>588225</v>
       </c>
       <c r="R12" t="n">
-        <v>6435993</v>
+        <v>6435968</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118597574</v>
+        <v>118594819</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588227</v>
+        <v>588240</v>
       </c>
       <c r="R13" t="n">
-        <v>6435928</v>
+        <v>6435993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118594955</v>
+        <v>118597574</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588225</v>
+        <v>588227</v>
       </c>
       <c r="R14" t="n">
-        <v>6435968</v>
+        <v>6435928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118597065</v>
+        <v>118597239</v>
       </c>
       <c r="B17" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,35 +2364,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588304</v>
+        <v>588323</v>
       </c>
       <c r="R17" t="n">
-        <v>6436063</v>
+        <v>6436028</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,17 +2438,13 @@
           <t>2024-07-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2467,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118597293</v>
+        <v>118597267</v>
       </c>
       <c r="B18" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,38 +2475,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2518,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588360</v>
+        <v>588348</v>
       </c>
       <c r="R18" t="n">
-        <v>6436048</v>
+        <v>6436039</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118597239</v>
+        <v>118597293</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2593,35 +2586,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2629,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588323</v>
+        <v>588360</v>
       </c>
       <c r="R19" t="n">
-        <v>6436028</v>
+        <v>6436048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,10 +2688,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118597267</v>
+        <v>118597065</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,35 +2700,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2740,13 +2736,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588348</v>
+        <v>588304</v>
       </c>
       <c r="R20" t="n">
-        <v>6436039</v>
+        <v>6436063</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,13 +2774,17 @@
           <t>2024-07-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118594834</v>
+        <v>118597378</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,25 +3156,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588243</v>
+        <v>588349</v>
       </c>
       <c r="R24" t="n">
-        <v>6435983</v>
+        <v>6436020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118594734</v>
+        <v>118594834</v>
       </c>
       <c r="B25" t="n">
         <v>97846</v>
@@ -3299,14 +3299,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588223</v>
+        <v>588243</v>
       </c>
       <c r="R25" t="n">
-        <v>6435976</v>
+        <v>6435983</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,7 +3366,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118595018</v>
+        <v>118594734</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3410,14 +3410,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588242</v>
+        <v>588223</v>
       </c>
       <c r="R26" t="n">
-        <v>6435991</v>
+        <v>6435976</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118594488</v>
+        <v>118595018</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3511,12 +3511,12 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588214</v>
+        <v>588242</v>
       </c>
       <c r="R27" t="n">
-        <v>6435937</v>
+        <v>6435991</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118597378</v>
+        <v>118594488</v>
       </c>
       <c r="B28" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3600,34 +3600,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588349</v>
+        <v>588214</v>
       </c>
       <c r="R28" t="n">
-        <v>6436020</v>
+        <v>6435937</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118597410</v>
+        <v>118597598</v>
       </c>
       <c r="B53" t="n">
-        <v>94620</v>
+        <v>104940</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6413,26 +6413,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6441,10 +6449,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>588363</v>
+        <v>588224</v>
       </c>
       <c r="R53" t="n">
-        <v>6436008</v>
+        <v>6435937</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6837,10 +6845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118597598</v>
+        <v>118597410</v>
       </c>
       <c r="B57" t="n">
-        <v>104940</v>
+        <v>94620</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6853,34 +6861,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>588224</v>
+        <v>588363</v>
       </c>
       <c r="R57" t="n">
-        <v>6435937</v>
+        <v>6436008</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118660036</v>
+        <v>118659823</v>
       </c>
       <c r="B67" t="n">
         <v>97846</v>
@@ -7998,11 +7998,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -8011,10 +8007,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>588380</v>
+        <v>588322</v>
       </c>
       <c r="R67" t="n">
-        <v>6435970</v>
+        <v>6435984</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8074,7 +8070,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118659823</v>
+        <v>118660036</v>
       </c>
       <c r="B68" t="n">
         <v>97846</v>
@@ -8113,7 +8109,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -8122,10 +8122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>588322</v>
+        <v>588380</v>
       </c>
       <c r="R68" t="n">
-        <v>6435984</v>
+        <v>6435970</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118660013</v>
+        <v>118659809</v>
       </c>
       <c r="B69" t="n">
         <v>97846</v>
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588383</v>
+        <v>588355</v>
       </c>
       <c r="R69" t="n">
-        <v>6435986</v>
+        <v>6436008</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118659809</v>
+        <v>118659790</v>
       </c>
       <c r="B70" t="n">
         <v>97846</v>
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588355</v>
+        <v>588326</v>
       </c>
       <c r="R70" t="n">
-        <v>6436008</v>
+        <v>6436033</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118659790</v>
+        <v>118660013</v>
       </c>
       <c r="B71" t="n">
         <v>97846</v>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588326</v>
+        <v>588383</v>
       </c>
       <c r="R71" t="n">
-        <v>6436033</v>
+        <v>6435986</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8628,10 +8628,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118659848</v>
+        <v>118596695</v>
       </c>
       <c r="B73" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8644,31 +8644,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8676,10 +8679,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>588419</v>
+        <v>588270</v>
       </c>
       <c r="R73" t="n">
-        <v>6435987</v>
+        <v>6436044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8706,12 +8709,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8739,10 +8742,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118596695</v>
+        <v>118659848</v>
       </c>
       <c r="B74" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8755,34 +8758,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>588270</v>
+        <v>588419</v>
       </c>
       <c r="R74" t="n">
-        <v>6436044</v>
+        <v>6435987</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9186,10 +9186,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118660618</v>
+        <v>118596742</v>
       </c>
       <c r="B78" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9202,35 +9202,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9238,10 +9237,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588407</v>
+        <v>588295</v>
       </c>
       <c r="R78" t="n">
-        <v>6435952</v>
+        <v>6436033</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9268,12 +9267,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9301,10 +9300,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118596742</v>
+        <v>118660618</v>
       </c>
       <c r="B79" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9317,34 +9316,35 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>588295</v>
+        <v>588407</v>
       </c>
       <c r="R79" t="n">
-        <v>6436033</v>
+        <v>6435952</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118596776</v>
+        <v>118597504</v>
       </c>
       <c r="B2" t="n">
-        <v>104940</v>
+        <v>90908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588272</v>
+        <v>588334</v>
       </c>
       <c r="R2" t="n">
-        <v>6436033</v>
+        <v>6436022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118597219</v>
+        <v>118597136</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588317</v>
+        <v>588295</v>
       </c>
       <c r="R3" t="n">
-        <v>6436035</v>
+        <v>6436061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118597187</v>
+        <v>118597267</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -949,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588288</v>
+        <v>588348</v>
       </c>
       <c r="R4" t="n">
-        <v>6436050</v>
+        <v>6436039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118597451</v>
+        <v>118594743</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1060,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588350</v>
+        <v>588239</v>
       </c>
       <c r="R5" t="n">
-        <v>6436007</v>
+        <v>6436002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118597484</v>
+        <v>118596776</v>
       </c>
       <c r="B6" t="n">
         <v>104940</v>
@@ -1171,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588339</v>
+        <v>588272</v>
       </c>
       <c r="R6" t="n">
-        <v>6436034</v>
+        <v>6436033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118594699</v>
+        <v>118594511</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1273,19 +1275,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374, Långgölen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588208</v>
+        <v>588220</v>
       </c>
       <c r="R7" t="n">
-        <v>6435965</v>
+        <v>6435969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118594991</v>
+        <v>118597392</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1384,11 +1390,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1397,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588220</v>
+        <v>588372</v>
       </c>
       <c r="R8" t="n">
-        <v>6435964</v>
+        <v>6436011</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118596948</v>
+        <v>118594834</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1508,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588269</v>
+        <v>588243</v>
       </c>
       <c r="R9" t="n">
-        <v>6436070</v>
+        <v>6435983</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1573,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118594794</v>
+        <v>118597432</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1610,11 +1612,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1623,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588252</v>
+        <v>588370</v>
       </c>
       <c r="R10" t="n">
-        <v>6435994</v>
+        <v>6436006</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118597164</v>
+        <v>118597293</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,35 +1696,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1734,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588296</v>
+        <v>588360</v>
       </c>
       <c r="R11" t="n">
-        <v>6436035</v>
+        <v>6436048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118594955</v>
+        <v>118597118</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1845,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588225</v>
+        <v>588306</v>
       </c>
       <c r="R12" t="n">
-        <v>6435968</v>
+        <v>6436055</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1909,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118594819</v>
+        <v>118594857</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1956,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588240</v>
+        <v>588230</v>
       </c>
       <c r="R13" t="n">
-        <v>6435993</v>
+        <v>6435980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118597574</v>
+        <v>118594488</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2053,12 +2054,12 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2067,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588227</v>
+        <v>588214</v>
       </c>
       <c r="R14" t="n">
-        <v>6435928</v>
+        <v>6435937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118594896</v>
+        <v>118597469</v>
       </c>
       <c r="B15" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588223</v>
+        <v>588317</v>
       </c>
       <c r="R15" t="n">
-        <v>6435976</v>
+        <v>6435988</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2242,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118597118</v>
+        <v>118596857</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2280,19 +2281,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A  27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588306</v>
+        <v>588255</v>
       </c>
       <c r="R16" t="n">
-        <v>6436055</v>
+        <v>6436028</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118597239</v>
+        <v>118596899</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2386,12 +2391,12 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2400,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588323</v>
+        <v>588276</v>
       </c>
       <c r="R17" t="n">
-        <v>6436028</v>
+        <v>6436025</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118597267</v>
+        <v>118597187</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588348</v>
+        <v>588288</v>
       </c>
       <c r="R18" t="n">
-        <v>6436039</v>
+        <v>6436050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118597293</v>
+        <v>118594658</v>
       </c>
       <c r="B19" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,38 +2591,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2625,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588360</v>
+        <v>588211</v>
       </c>
       <c r="R19" t="n">
-        <v>6436048</v>
+        <v>6435962</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118597065</v>
+        <v>118594849</v>
       </c>
       <c r="B20" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2700,35 +2702,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2736,13 +2742,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588304</v>
+        <v>588235</v>
       </c>
       <c r="R20" t="n">
-        <v>6436063</v>
+        <v>6435981</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,17 +2780,13 @@
           <t>2024-07-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2803,7 +2805,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118594936</v>
+        <v>118597524</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2842,11 +2844,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2855,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588234</v>
+        <v>588256</v>
       </c>
       <c r="R21" t="n">
-        <v>6435965</v>
+        <v>6436024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2918,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118594683</v>
+        <v>118594955</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -2957,23 +2955,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588206</v>
+        <v>588225</v>
       </c>
       <c r="R22" t="n">
-        <v>6435960</v>
+        <v>6435968</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3033,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118597458</v>
+        <v>118594936</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -3072,7 +3066,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3081,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588342</v>
+        <v>588234</v>
       </c>
       <c r="R23" t="n">
-        <v>6436015</v>
+        <v>6435965</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3144,10 +3142,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118597378</v>
+        <v>118596948</v>
       </c>
       <c r="B24" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,25 +3154,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588349</v>
+        <v>588269</v>
       </c>
       <c r="R24" t="n">
-        <v>6436020</v>
+        <v>6436070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118594834</v>
+        <v>118597410</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,33 +3265,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3303,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588243</v>
+        <v>588363</v>
       </c>
       <c r="R25" t="n">
-        <v>6435983</v>
+        <v>6436008</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,7 +3360,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118594734</v>
+        <v>118596804</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3405,19 +3399,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588223</v>
+        <v>588239</v>
       </c>
       <c r="R26" t="n">
-        <v>6435976</v>
+        <v>6436018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3475,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118595018</v>
+        <v>118597100</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3525,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588242</v>
+        <v>588307</v>
       </c>
       <c r="R27" t="n">
-        <v>6435991</v>
+        <v>6436069</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3588,7 +3586,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118594488</v>
+        <v>118594446</v>
       </c>
       <c r="B28" t="n">
         <v>97846</v>
@@ -3622,7 +3620,11 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -3636,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588214</v>
+        <v>588224</v>
       </c>
       <c r="R28" t="n">
-        <v>6435937</v>
+        <v>6435907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3699,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118594849</v>
+        <v>118594896</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3711,25 +3713,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3738,11 +3740,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3751,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588235</v>
+        <v>588223</v>
       </c>
       <c r="R29" t="n">
-        <v>6435981</v>
+        <v>6435976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,7 +3812,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118596651</v>
+        <v>118597239</v>
       </c>
       <c r="B30" t="n">
         <v>97846</v>
@@ -3862,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588258</v>
+        <v>588323</v>
       </c>
       <c r="R30" t="n">
-        <v>6435987</v>
+        <v>6436028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3925,7 +3923,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118597432</v>
+        <v>118597343</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3973,10 +3971,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588370</v>
+        <v>588368</v>
       </c>
       <c r="R31" t="n">
-        <v>6436006</v>
+        <v>6436025</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118597504</v>
+        <v>118596651</v>
       </c>
       <c r="B32" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4048,38 +4046,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4087,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588334</v>
+        <v>588258</v>
       </c>
       <c r="R32" t="n">
-        <v>6436022</v>
+        <v>6435987</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118597136</v>
+        <v>118596922</v>
       </c>
       <c r="B33" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4162,38 +4157,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4201,10 +4193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588295</v>
+        <v>588264</v>
       </c>
       <c r="R33" t="n">
-        <v>6436061</v>
+        <v>6436046</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118597539</v>
+        <v>118597065</v>
       </c>
       <c r="B34" t="n">
-        <v>104940</v>
+        <v>57306</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,35 +4268,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4312,13 +4304,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588236</v>
+        <v>588304</v>
       </c>
       <c r="R34" t="n">
-        <v>6436001</v>
+        <v>6436063</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4350,13 +4342,17 @@
           <t>2024-07-21</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4375,7 +4371,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118597524</v>
+        <v>118594459</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4423,10 +4419,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588256</v>
+        <v>588238</v>
       </c>
       <c r="R35" t="n">
-        <v>6436024</v>
+        <v>6435934</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4486,7 +4482,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118594763</v>
+        <v>118597164</v>
       </c>
       <c r="B36" t="n">
         <v>97846</v>
@@ -4534,10 +4530,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588231</v>
+        <v>588296</v>
       </c>
       <c r="R36" t="n">
-        <v>6435990</v>
+        <v>6436035</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4597,7 +4593,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118596922</v>
+        <v>118597574</v>
       </c>
       <c r="B37" t="n">
         <v>97846</v>
@@ -4645,10 +4641,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588264</v>
+        <v>588227</v>
       </c>
       <c r="R37" t="n">
-        <v>6436046</v>
+        <v>6435928</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4708,7 +4704,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118597100</v>
+        <v>118597561</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4747,7 +4743,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588307</v>
+        <v>588237</v>
       </c>
       <c r="R38" t="n">
-        <v>6436069</v>
+        <v>6435907</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118597252</v>
+        <v>118597015</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588324</v>
+        <v>588316</v>
       </c>
       <c r="R39" t="n">
-        <v>6436038</v>
+        <v>6436073</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118597561</v>
+        <v>118595018</v>
       </c>
       <c r="B40" t="n">
         <v>97846</v>
@@ -4969,11 +4969,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4982,10 +4978,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588237</v>
+        <v>588242</v>
       </c>
       <c r="R40" t="n">
-        <v>6435907</v>
+        <v>6435991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5045,7 +5041,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118596804</v>
+        <v>118597252</v>
       </c>
       <c r="B41" t="n">
         <v>97846</v>
@@ -5084,11 +5080,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -5097,10 +5089,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588239</v>
+        <v>588324</v>
       </c>
       <c r="R41" t="n">
-        <v>6436018</v>
+        <v>6436038</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5160,10 +5152,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118596857</v>
+        <v>118597378</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,25 +5164,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5199,23 +5191,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A  27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588255</v>
+        <v>588349</v>
       </c>
       <c r="R42" t="n">
-        <v>6436028</v>
+        <v>6436020</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5275,10 +5263,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118594511</v>
+        <v>118597539</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5287,25 +5275,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5314,23 +5302,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 27374, Långgölen, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588220</v>
+        <v>588236</v>
       </c>
       <c r="R43" t="n">
-        <v>6435969</v>
+        <v>6436001</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5390,7 +5374,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118594446</v>
+        <v>118594819</v>
       </c>
       <c r="B44" t="n">
         <v>97846</v>
@@ -5429,11 +5413,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5442,10 +5422,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588224</v>
+        <v>588240</v>
       </c>
       <c r="R44" t="n">
-        <v>6435907</v>
+        <v>6435993</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5505,7 +5485,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118594721</v>
+        <v>118597458</v>
       </c>
       <c r="B45" t="n">
         <v>97846</v>
@@ -5544,11 +5524,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5557,10 +5533,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588225</v>
+        <v>588342</v>
       </c>
       <c r="R45" t="n">
-        <v>6435977</v>
+        <v>6436015</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5620,7 +5596,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118597392</v>
+        <v>118594794</v>
       </c>
       <c r="B46" t="n">
         <v>97846</v>
@@ -5659,7 +5635,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5668,10 +5648,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>588372</v>
+        <v>588252</v>
       </c>
       <c r="R46" t="n">
-        <v>6436011</v>
+        <v>6435994</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5731,7 +5711,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118597015</v>
+        <v>118594683</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5770,19 +5750,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588316</v>
+        <v>588206</v>
       </c>
       <c r="R47" t="n">
-        <v>6436073</v>
+        <v>6435960</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,7 +5826,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118594658</v>
+        <v>118596628</v>
       </c>
       <c r="B48" t="n">
         <v>97846</v>
@@ -5876,12 +5860,12 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -5890,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588211</v>
+        <v>588242</v>
       </c>
       <c r="R48" t="n">
-        <v>6435962</v>
+        <v>6436014</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5953,7 +5937,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118594743</v>
+        <v>118594721</v>
       </c>
       <c r="B49" t="n">
         <v>97846</v>
@@ -5992,7 +5976,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -6001,10 +5989,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>588239</v>
+        <v>588225</v>
       </c>
       <c r="R49" t="n">
-        <v>6436002</v>
+        <v>6435977</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6064,7 +6052,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118597469</v>
+        <v>118597219</v>
       </c>
       <c r="B50" t="n">
         <v>97846</v>
@@ -6103,7 +6091,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -6115,7 +6107,7 @@
         <v>588317</v>
       </c>
       <c r="R50" t="n">
-        <v>6435988</v>
+        <v>6436035</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6175,7 +6167,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118594459</v>
+        <v>118594699</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -6223,10 +6215,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588238</v>
+        <v>588208</v>
       </c>
       <c r="R51" t="n">
-        <v>6435934</v>
+        <v>6435965</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6286,7 +6278,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118596899</v>
+        <v>118594734</v>
       </c>
       <c r="B52" t="n">
         <v>97846</v>
@@ -6320,24 +6312,24 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>588276</v>
+        <v>588223</v>
       </c>
       <c r="R52" t="n">
-        <v>6436025</v>
+        <v>6435976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6397,10 +6389,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118597598</v>
+        <v>118597451</v>
       </c>
       <c r="B53" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6409,25 +6401,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6436,11 +6428,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6449,10 +6437,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>588224</v>
+        <v>588350</v>
       </c>
       <c r="R53" t="n">
-        <v>6435937</v>
+        <v>6436007</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6512,7 +6500,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118597343</v>
+        <v>118594991</v>
       </c>
       <c r="B54" t="n">
         <v>97846</v>
@@ -6551,7 +6539,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -6560,10 +6552,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588368</v>
+        <v>588220</v>
       </c>
       <c r="R54" t="n">
-        <v>6436025</v>
+        <v>6435964</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6623,7 +6615,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118594857</v>
+        <v>118594763</v>
       </c>
       <c r="B55" t="n">
         <v>97846</v>
@@ -6671,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588230</v>
+        <v>588231</v>
       </c>
       <c r="R55" t="n">
-        <v>6435980</v>
+        <v>6435990</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6734,10 +6726,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118596628</v>
+        <v>118597598</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6746,32 +6738,36 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -6782,10 +6778,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>588242</v>
+        <v>588224</v>
       </c>
       <c r="R56" t="n">
-        <v>6436014</v>
+        <v>6435937</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6845,10 +6841,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118597410</v>
+        <v>118597484</v>
       </c>
       <c r="B57" t="n">
-        <v>94620</v>
+        <v>104940</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6861,25 +6857,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>588363</v>
+        <v>588339</v>
       </c>
       <c r="R57" t="n">
-        <v>6436008</v>
+        <v>6436034</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118659974</v>
+        <v>118660618</v>
       </c>
       <c r="B58" t="n">
         <v>97846</v>
@@ -6991,7 +6991,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7000,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>588387</v>
+        <v>588407</v>
       </c>
       <c r="R58" t="n">
-        <v>6435972</v>
+        <v>6435952</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7063,7 +7067,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118659907</v>
+        <v>118659989</v>
       </c>
       <c r="B59" t="n">
         <v>97846</v>
@@ -7111,10 +7115,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>588400</v>
+        <v>588391</v>
       </c>
       <c r="R59" t="n">
-        <v>6435993</v>
+        <v>6435977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7174,7 +7178,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118659945</v>
+        <v>118659790</v>
       </c>
       <c r="B60" t="n">
         <v>97846</v>
@@ -7222,10 +7226,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588429</v>
+        <v>588326</v>
       </c>
       <c r="R60" t="n">
-        <v>6435973</v>
+        <v>6436033</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7285,10 +7289,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118659872</v>
+        <v>118596728</v>
       </c>
       <c r="B61" t="n">
-        <v>104940</v>
+        <v>89999</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7297,35 +7301,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>2051</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7333,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>588386</v>
+        <v>588287</v>
       </c>
       <c r="R61" t="n">
-        <v>6436004</v>
+        <v>6436027</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7363,12 +7370,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7396,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118596680</v>
+        <v>118659809</v>
       </c>
       <c r="B62" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7412,34 +7419,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7447,10 +7451,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>588251</v>
+        <v>588355</v>
       </c>
       <c r="R62" t="n">
-        <v>6436043</v>
+        <v>6436008</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7477,12 +7481,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7510,10 +7514,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118659964</v>
+        <v>118659872</v>
       </c>
       <c r="B63" t="n">
-        <v>94620</v>
+        <v>104940</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7526,25 +7530,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7554,10 +7562,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>588411</v>
+        <v>588386</v>
       </c>
       <c r="R63" t="n">
-        <v>6435983</v>
+        <v>6436004</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7617,10 +7625,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118660053</v>
+        <v>118596680</v>
       </c>
       <c r="B64" t="n">
-        <v>91823</v>
+        <v>89999</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7629,30 +7637,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7668,10 +7676,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588406</v>
+        <v>588251</v>
       </c>
       <c r="R64" t="n">
-        <v>6435986</v>
+        <v>6436043</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7698,12 +7706,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7731,10 +7739,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118596728</v>
+        <v>118659907</v>
       </c>
       <c r="B65" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7747,34 +7755,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7782,10 +7787,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588287</v>
+        <v>588400</v>
       </c>
       <c r="R65" t="n">
-        <v>6436027</v>
+        <v>6435993</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7812,12 +7817,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7845,10 +7850,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118596709</v>
+        <v>118659974</v>
       </c>
       <c r="B66" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7861,34 +7866,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7896,10 +7898,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>588280</v>
+        <v>588387</v>
       </c>
       <c r="R66" t="n">
-        <v>6436028</v>
+        <v>6435972</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7926,12 +7928,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8070,10 +8072,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118660036</v>
+        <v>118596709</v>
       </c>
       <c r="B68" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8086,35 +8088,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8122,10 +8123,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>588380</v>
+        <v>588280</v>
       </c>
       <c r="R68" t="n">
-        <v>6435970</v>
+        <v>6436028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8152,12 +8153,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8185,7 +8186,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118659809</v>
+        <v>118659848</v>
       </c>
       <c r="B69" t="n">
         <v>97846</v>
@@ -8233,10 +8234,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588355</v>
+        <v>588419</v>
       </c>
       <c r="R69" t="n">
-        <v>6436008</v>
+        <v>6435987</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8296,10 +8297,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118659790</v>
+        <v>118596742</v>
       </c>
       <c r="B70" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8312,31 +8313,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8344,7 +8348,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588326</v>
+        <v>588295</v>
       </c>
       <c r="R70" t="n">
         <v>6436033</v>
@@ -8374,12 +8378,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8407,7 +8411,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118660013</v>
+        <v>118659892</v>
       </c>
       <c r="B71" t="n">
         <v>97846</v>
@@ -8455,10 +8459,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588383</v>
+        <v>588413</v>
       </c>
       <c r="R71" t="n">
-        <v>6435986</v>
+        <v>6435984</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8628,10 +8632,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118596695</v>
+        <v>118660013</v>
       </c>
       <c r="B73" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8644,34 +8648,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8679,10 +8680,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>588270</v>
+        <v>588383</v>
       </c>
       <c r="R73" t="n">
-        <v>6436044</v>
+        <v>6435986</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8709,12 +8710,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8742,7 +8743,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118659848</v>
+        <v>118660036</v>
       </c>
       <c r="B74" t="n">
         <v>97846</v>
@@ -8781,7 +8782,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -8790,10 +8795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>588419</v>
+        <v>588380</v>
       </c>
       <c r="R74" t="n">
-        <v>6435987</v>
+        <v>6435970</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8853,10 +8858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118659989</v>
+        <v>118660053</v>
       </c>
       <c r="B75" t="n">
-        <v>97846</v>
+        <v>91823</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8865,35 +8870,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8901,10 +8909,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>588391</v>
+        <v>588406</v>
       </c>
       <c r="R75" t="n">
-        <v>6435977</v>
+        <v>6435986</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8964,10 +8972,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118659892</v>
+        <v>118596695</v>
       </c>
       <c r="B76" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8980,31 +8988,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9012,10 +9023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>588413</v>
+        <v>588270</v>
       </c>
       <c r="R76" t="n">
-        <v>6435984</v>
+        <v>6436044</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9042,12 +9053,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9075,10 +9086,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118659916</v>
+        <v>118659964</v>
       </c>
       <c r="B77" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9087,33 +9098,29 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -9123,10 +9130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>588419</v>
+        <v>588411</v>
       </c>
       <c r="R77" t="n">
-        <v>6435978</v>
+        <v>6435983</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9186,10 +9193,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118596742</v>
+        <v>118659945</v>
       </c>
       <c r="B78" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9202,34 +9209,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9237,10 +9241,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588295</v>
+        <v>588429</v>
       </c>
       <c r="R78" t="n">
-        <v>6436033</v>
+        <v>6435973</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9267,12 +9271,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9300,7 +9304,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118660618</v>
+        <v>118659916</v>
       </c>
       <c r="B79" t="n">
         <v>97846</v>
@@ -9339,11 +9343,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>588407</v>
+        <v>588419</v>
       </c>
       <c r="R79" t="n">
-        <v>6435952</v>
+        <v>6435978</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118597504</v>
+        <v>118597252</v>
       </c>
       <c r="B2" t="n">
-        <v>90908</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588334</v>
+        <v>588324</v>
       </c>
       <c r="R2" t="n">
-        <v>6436022</v>
+        <v>6436038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118597136</v>
+        <v>118594699</v>
       </c>
       <c r="B3" t="n">
-        <v>90908</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588295</v>
+        <v>588208</v>
       </c>
       <c r="R3" t="n">
-        <v>6436061</v>
+        <v>6435965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118597267</v>
+        <v>118597293</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>90915</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588348</v>
+        <v>588360</v>
       </c>
       <c r="R4" t="n">
-        <v>6436039</v>
+        <v>6436048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118594743</v>
+        <v>118596651</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588239</v>
+        <v>588258</v>
       </c>
       <c r="R5" t="n">
-        <v>6436002</v>
+        <v>6435987</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118596776</v>
+        <v>118594857</v>
       </c>
       <c r="B6" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588272</v>
+        <v>588230</v>
       </c>
       <c r="R6" t="n">
-        <v>6436033</v>
+        <v>6435980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118594511</v>
+        <v>118595018</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,23 +1272,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27374, Långgölen, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588220</v>
+        <v>588242</v>
       </c>
       <c r="R7" t="n">
-        <v>6435969</v>
+        <v>6435991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118597392</v>
+        <v>118596922</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588372</v>
+        <v>588264</v>
       </c>
       <c r="R8" t="n">
-        <v>6436011</v>
+        <v>6436046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118594834</v>
+        <v>118594459</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588243</v>
+        <v>588238</v>
       </c>
       <c r="R9" t="n">
-        <v>6435983</v>
+        <v>6435934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118597432</v>
+        <v>118597164</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588370</v>
+        <v>588296</v>
       </c>
       <c r="R10" t="n">
-        <v>6436006</v>
+        <v>6436035</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118597293</v>
+        <v>118597267</v>
       </c>
       <c r="B11" t="n">
-        <v>90908</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,38 +1689,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588360</v>
+        <v>588348</v>
       </c>
       <c r="R11" t="n">
-        <v>6436048</v>
+        <v>6436039</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118597118</v>
+        <v>118597343</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588306</v>
+        <v>588368</v>
       </c>
       <c r="R12" t="n">
-        <v>6436055</v>
+        <v>6436025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118594857</v>
+        <v>118594896</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,25 +1911,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588230</v>
+        <v>588223</v>
       </c>
       <c r="R13" t="n">
-        <v>6435980</v>
+        <v>6435976</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118594488</v>
+        <v>118594743</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,12 +2044,12 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2068,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588214</v>
+        <v>588239</v>
       </c>
       <c r="R14" t="n">
-        <v>6435937</v>
+        <v>6436002</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118597469</v>
+        <v>118597219</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,7 +2160,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2182,7 +2176,7 @@
         <v>588317</v>
       </c>
       <c r="R15" t="n">
-        <v>6435988</v>
+        <v>6436035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118596857</v>
+        <v>118596628</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,11 +2270,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2290,14 +2280,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A  27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588255</v>
+        <v>588242</v>
       </c>
       <c r="R16" t="n">
-        <v>6436028</v>
+        <v>6436014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118596899</v>
+        <v>118594488</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588276</v>
+        <v>588214</v>
       </c>
       <c r="R17" t="n">
-        <v>6436025</v>
+        <v>6435937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118597187</v>
+        <v>118594936</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,7 +2497,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2516,10 +2510,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588288</v>
+        <v>588234</v>
       </c>
       <c r="R18" t="n">
-        <v>6436050</v>
+        <v>6435965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118594658</v>
+        <v>118594819</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588211</v>
+        <v>588240</v>
       </c>
       <c r="R19" t="n">
-        <v>6435962</v>
+        <v>6435993</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118594849</v>
+        <v>118597015</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,11 +2723,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2742,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588235</v>
+        <v>588316</v>
       </c>
       <c r="R20" t="n">
-        <v>6435981</v>
+        <v>6436073</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118597524</v>
+        <v>118596899</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,12 +2829,12 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2853,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588256</v>
+        <v>588276</v>
       </c>
       <c r="R21" t="n">
-        <v>6436024</v>
+        <v>6436025</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2906,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118594955</v>
+        <v>118596990</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,7 +2945,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2964,10 +2958,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588225</v>
+        <v>588269</v>
       </c>
       <c r="R22" t="n">
-        <v>6435968</v>
+        <v>6436070</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3021,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118594936</v>
+        <v>118597598</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3033,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3068,7 +3062,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3079,10 +3073,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588234</v>
+        <v>588224</v>
       </c>
       <c r="R23" t="n">
-        <v>6435965</v>
+        <v>6435937</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3142,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118596948</v>
+        <v>118597469</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588269</v>
+        <v>588317</v>
       </c>
       <c r="R24" t="n">
-        <v>6436070</v>
+        <v>6435988</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118597410</v>
+        <v>118594834</v>
       </c>
       <c r="B25" t="n">
-        <v>94620</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3265,29 +3259,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3297,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588363</v>
+        <v>588243</v>
       </c>
       <c r="R25" t="n">
-        <v>6436008</v>
+        <v>6435983</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3360,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118596804</v>
+        <v>118594446</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3412,10 +3410,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588239</v>
+        <v>588224</v>
       </c>
       <c r="R26" t="n">
-        <v>6436018</v>
+        <v>6435907</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118597100</v>
+        <v>118597392</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3523,10 +3521,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588307</v>
+        <v>588372</v>
       </c>
       <c r="R27" t="n">
-        <v>6436069</v>
+        <v>6436011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,10 +3584,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118594446</v>
+        <v>118597378</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3598,25 +3596,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3625,11 +3623,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3638,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588224</v>
+        <v>588349</v>
       </c>
       <c r="R28" t="n">
-        <v>6435907</v>
+        <v>6436020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,10 +3695,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118594896</v>
+        <v>118594658</v>
       </c>
       <c r="B29" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,25 +3707,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3749,10 +3743,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588223</v>
+        <v>588211</v>
       </c>
       <c r="R29" t="n">
-        <v>6435976</v>
+        <v>6435962</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,10 +3806,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118597239</v>
+        <v>118594991</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3851,7 +3845,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3860,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588323</v>
+        <v>588220</v>
       </c>
       <c r="R30" t="n">
-        <v>6436028</v>
+        <v>6435964</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3923,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118597343</v>
+        <v>118597539</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3935,25 +3933,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3971,10 +3969,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588368</v>
+        <v>588236</v>
       </c>
       <c r="R31" t="n">
-        <v>6436025</v>
+        <v>6436001</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4034,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118596651</v>
+        <v>118594721</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4073,7 +4071,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4082,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588258</v>
+        <v>588225</v>
       </c>
       <c r="R32" t="n">
-        <v>6435987</v>
+        <v>6435977</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4145,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118596922</v>
+        <v>118597504</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>90915</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,35 +4159,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588264</v>
+        <v>588334</v>
       </c>
       <c r="R33" t="n">
-        <v>6436046</v>
+        <v>6436022</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4371,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118594459</v>
+        <v>118594849</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,7 +4415,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4419,10 +4428,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588238</v>
+        <v>588235</v>
       </c>
       <c r="R35" t="n">
-        <v>6435934</v>
+        <v>6435981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4482,10 +4491,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118597164</v>
+        <v>118597458</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4530,10 +4539,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588296</v>
+        <v>588342</v>
       </c>
       <c r="R36" t="n">
-        <v>6436035</v>
+        <v>6436015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4593,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118597574</v>
+        <v>118597187</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4641,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588227</v>
+        <v>588288</v>
       </c>
       <c r="R37" t="n">
-        <v>6435928</v>
+        <v>6436050</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,10 +4713,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118597561</v>
+        <v>118594734</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,23 +4752,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588237</v>
+        <v>588223</v>
       </c>
       <c r="R38" t="n">
-        <v>6435907</v>
+        <v>6435976</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4819,10 +4824,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118597015</v>
+        <v>118597484</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4831,25 +4836,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4867,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588316</v>
+        <v>588339</v>
       </c>
       <c r="R39" t="n">
-        <v>6436073</v>
+        <v>6436034</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4930,10 +4935,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118595018</v>
+        <v>118597136</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>90915</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4942,35 +4947,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4978,10 +4986,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588242</v>
+        <v>588295</v>
       </c>
       <c r="R40" t="n">
-        <v>6435991</v>
+        <v>6436061</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,10 +5049,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118597252</v>
+        <v>118597239</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5089,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588324</v>
+        <v>588323</v>
       </c>
       <c r="R41" t="n">
-        <v>6436038</v>
+        <v>6436028</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5152,10 +5160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118597378</v>
+        <v>118594794</v>
       </c>
       <c r="B42" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5164,25 +5172,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5191,7 +5199,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5200,10 +5212,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588349</v>
+        <v>588252</v>
       </c>
       <c r="R42" t="n">
-        <v>6436020</v>
+        <v>6435994</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5263,10 +5275,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118597539</v>
+        <v>118594683</v>
       </c>
       <c r="B43" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5275,25 +5287,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5302,19 +5314,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588236</v>
+        <v>588206</v>
       </c>
       <c r="R43" t="n">
-        <v>6436001</v>
+        <v>6435960</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5374,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118594819</v>
+        <v>118597574</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5422,10 +5438,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588240</v>
+        <v>588227</v>
       </c>
       <c r="R44" t="n">
-        <v>6435993</v>
+        <v>6435928</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5485,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118597458</v>
+        <v>118594511</v>
       </c>
       <c r="B45" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5524,19 +5540,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374, Långgölen, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588342</v>
+        <v>588220</v>
       </c>
       <c r="R45" t="n">
-        <v>6436015</v>
+        <v>6435969</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5596,10 +5616,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118594794</v>
+        <v>118597118</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5635,11 +5655,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5648,10 +5664,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>588252</v>
+        <v>588306</v>
       </c>
       <c r="R46" t="n">
-        <v>6435994</v>
+        <v>6436055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5711,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118594683</v>
+        <v>118597100</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5750,23 +5766,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588206</v>
+        <v>588307</v>
       </c>
       <c r="R47" t="n">
-        <v>6435960</v>
+        <v>6436069</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5826,10 +5838,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118596628</v>
+        <v>118596857</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5860,7 +5872,11 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5870,14 +5886,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A  27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588242</v>
+        <v>588255</v>
       </c>
       <c r="R48" t="n">
-        <v>6436014</v>
+        <v>6436028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5937,10 +5953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118594721</v>
+        <v>118597410</v>
       </c>
       <c r="B49" t="n">
-        <v>97846</v>
+        <v>94627</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5949,38 +5965,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5989,10 +5997,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>588225</v>
+        <v>588363</v>
       </c>
       <c r="R49" t="n">
-        <v>6435977</v>
+        <v>6436008</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6052,10 +6060,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118597219</v>
+        <v>118597451</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6091,11 +6099,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -6104,10 +6108,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>588317</v>
+        <v>588350</v>
       </c>
       <c r="R50" t="n">
-        <v>6436035</v>
+        <v>6436007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6167,10 +6171,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118594699</v>
+        <v>118597524</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6215,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588208</v>
+        <v>588256</v>
       </c>
       <c r="R51" t="n">
-        <v>6435965</v>
+        <v>6436024</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6278,10 +6282,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118594734</v>
+        <v>118596776</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6290,25 +6294,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6322,14 +6326,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>588223</v>
+        <v>588272</v>
       </c>
       <c r="R52" t="n">
-        <v>6435976</v>
+        <v>6436033</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6389,10 +6393,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118597451</v>
+        <v>118594955</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6437,10 +6441,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>588350</v>
+        <v>588225</v>
       </c>
       <c r="R53" t="n">
-        <v>6436007</v>
+        <v>6435968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6500,10 +6504,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118594991</v>
+        <v>118594763</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6539,11 +6543,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -6552,10 +6552,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588220</v>
+        <v>588231</v>
       </c>
       <c r="R54" t="n">
-        <v>6435964</v>
+        <v>6435990</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,10 +6615,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118594763</v>
+        <v>118597561</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6654,7 +6654,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6663,10 +6667,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588231</v>
+        <v>588237</v>
       </c>
       <c r="R55" t="n">
-        <v>6435990</v>
+        <v>6435907</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6726,10 +6730,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118597598</v>
+        <v>118597432</v>
       </c>
       <c r="B56" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6738,25 +6742,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6765,11 +6769,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>588224</v>
+        <v>588370</v>
       </c>
       <c r="R56" t="n">
-        <v>6435937</v>
+        <v>6436006</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118597484</v>
+        <v>118596804</v>
       </c>
       <c r="B57" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6853,25 +6853,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6880,7 +6880,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6889,10 +6893,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>588339</v>
+        <v>588239</v>
       </c>
       <c r="R57" t="n">
-        <v>6436034</v>
+        <v>6436018</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6952,10 +6956,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118660618</v>
+        <v>118596728</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
+        <v>90006</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6968,35 +6972,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7004,10 +7007,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>588407</v>
+        <v>588287</v>
       </c>
       <c r="R58" t="n">
-        <v>6435952</v>
+        <v>6436027</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7034,12 +7037,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7067,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118659989</v>
+        <v>118659974</v>
       </c>
       <c r="B59" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7115,10 +7118,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>588391</v>
+        <v>588387</v>
       </c>
       <c r="R59" t="n">
-        <v>6435977</v>
+        <v>6435972</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7178,10 +7181,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118659790</v>
+        <v>118659945</v>
       </c>
       <c r="B60" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7226,10 +7229,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588326</v>
+        <v>588429</v>
       </c>
       <c r="R60" t="n">
-        <v>6436033</v>
+        <v>6435973</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7289,10 +7292,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118596728</v>
+        <v>118660648</v>
       </c>
       <c r="B61" t="n">
-        <v>89999</v>
+        <v>91786</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7301,32 +7304,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2051</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7340,10 +7339,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>588287</v>
+        <v>588400</v>
       </c>
       <c r="R61" t="n">
-        <v>6436027</v>
+        <v>6435972</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7370,12 +7369,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,7 +7405,7 @@
         <v>118659809</v>
       </c>
       <c r="B62" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7514,10 +7513,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118659872</v>
+        <v>118659790</v>
       </c>
       <c r="B63" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7526,25 +7525,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7562,10 +7561,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>588386</v>
+        <v>588326</v>
       </c>
       <c r="R63" t="n">
-        <v>6436004</v>
+        <v>6436033</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7625,10 +7624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118596680</v>
+        <v>118596742</v>
       </c>
       <c r="B64" t="n">
-        <v>89999</v>
+        <v>90006</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7676,10 +7675,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588251</v>
+        <v>588295</v>
       </c>
       <c r="R64" t="n">
-        <v>6436043</v>
+        <v>6436033</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7739,10 +7738,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118659907</v>
+        <v>118659964</v>
       </c>
       <c r="B65" t="n">
-        <v>97846</v>
+        <v>94627</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7751,33 +7750,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7787,10 +7782,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588400</v>
+        <v>588411</v>
       </c>
       <c r="R65" t="n">
-        <v>6435993</v>
+        <v>6435983</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7850,10 +7845,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118659974</v>
+        <v>118660013</v>
       </c>
       <c r="B66" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7898,10 +7893,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>588387</v>
+        <v>588383</v>
       </c>
       <c r="R66" t="n">
-        <v>6435972</v>
+        <v>6435986</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7961,10 +7956,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118659823</v>
+        <v>118659916</v>
       </c>
       <c r="B67" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8009,10 +8004,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>588322</v>
+        <v>588419</v>
       </c>
       <c r="R67" t="n">
-        <v>6435984</v>
+        <v>6435978</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8072,10 +8067,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118596709</v>
+        <v>118659823</v>
       </c>
       <c r="B68" t="n">
-        <v>89999</v>
+        <v>97853</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8088,34 +8083,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8123,10 +8115,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>588280</v>
+        <v>588322</v>
       </c>
       <c r="R68" t="n">
-        <v>6436028</v>
+        <v>6435984</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8153,12 +8145,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8186,10 +8178,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118659848</v>
+        <v>118660618</v>
       </c>
       <c r="B69" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8225,7 +8217,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8234,10 +8230,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588419</v>
+        <v>588407</v>
       </c>
       <c r="R69" t="n">
-        <v>6435987</v>
+        <v>6435952</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8297,10 +8293,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118596742</v>
+        <v>118659907</v>
       </c>
       <c r="B70" t="n">
-        <v>89999</v>
+        <v>97853</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8313,34 +8309,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8348,10 +8341,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588295</v>
+        <v>588400</v>
       </c>
       <c r="R70" t="n">
-        <v>6436033</v>
+        <v>6435993</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8378,12 +8371,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8411,10 +8404,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118659892</v>
+        <v>118659872</v>
       </c>
       <c r="B71" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8423,25 +8416,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8459,10 +8452,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588413</v>
+        <v>588386</v>
       </c>
       <c r="R71" t="n">
-        <v>6435984</v>
+        <v>6436004</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8522,10 +8515,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118660648</v>
+        <v>118660036</v>
       </c>
       <c r="B72" t="n">
-        <v>91779</v>
+        <v>97853</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,34 +8527,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8569,10 +8567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>588400</v>
+        <v>588380</v>
       </c>
       <c r="R72" t="n">
-        <v>6435972</v>
+        <v>6435970</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8632,10 +8630,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118660013</v>
+        <v>118596695</v>
       </c>
       <c r="B73" t="n">
-        <v>97846</v>
+        <v>90006</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8648,31 +8646,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8680,10 +8681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>588383</v>
+        <v>588270</v>
       </c>
       <c r="R73" t="n">
-        <v>6435986</v>
+        <v>6436044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8710,12 +8711,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8743,10 +8744,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118660036</v>
+        <v>118659892</v>
       </c>
       <c r="B74" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8782,11 +8783,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -8795,10 +8792,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>588380</v>
+        <v>588413</v>
       </c>
       <c r="R74" t="n">
-        <v>6435970</v>
+        <v>6435984</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8858,10 +8855,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118660053</v>
+        <v>118596709</v>
       </c>
       <c r="B75" t="n">
-        <v>91823</v>
+        <v>90006</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8870,30 +8867,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8909,10 +8906,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>588406</v>
+        <v>588280</v>
       </c>
       <c r="R75" t="n">
-        <v>6435986</v>
+        <v>6436028</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8939,12 +8936,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8972,10 +8969,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118596695</v>
+        <v>118659848</v>
       </c>
       <c r="B76" t="n">
-        <v>89999</v>
+        <v>97853</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8988,34 +8985,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9023,10 +9017,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>588270</v>
+        <v>588419</v>
       </c>
       <c r="R76" t="n">
-        <v>6436044</v>
+        <v>6435987</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9053,12 +9047,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9086,10 +9080,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118659964</v>
+        <v>118660053</v>
       </c>
       <c r="B77" t="n">
-        <v>94620</v>
+        <v>91830</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9098,31 +9092,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9130,10 +9131,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>588411</v>
+        <v>588406</v>
       </c>
       <c r="R77" t="n">
-        <v>6435983</v>
+        <v>6435986</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9193,10 +9194,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118659945</v>
+        <v>118659989</v>
       </c>
       <c r="B78" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9241,10 +9242,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588429</v>
+        <v>588391</v>
       </c>
       <c r="R78" t="n">
-        <v>6435973</v>
+        <v>6435977</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9304,10 +9305,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118659916</v>
+        <v>118596680</v>
       </c>
       <c r="B79" t="n">
-        <v>97846</v>
+        <v>90006</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9320,31 +9321,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9352,10 +9356,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>588419</v>
+        <v>588251</v>
       </c>
       <c r="R79" t="n">
-        <v>6435978</v>
+        <v>6436043</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9382,12 +9386,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9418,7 +9422,7 @@
         <v>118726486</v>
       </c>
       <c r="B80" t="n">
-        <v>89999</v>
+        <v>90006</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9646,7 +9650,7 @@
         <v>118809011</v>
       </c>
       <c r="B82" t="n">
-        <v>104940</v>
+        <v>104947</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9757,7 +9761,7 @@
         <v>118808997</v>
       </c>
       <c r="B83" t="n">
-        <v>89999</v>
+        <v>90006</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -6956,10 +6956,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118596728</v>
+        <v>118659945</v>
       </c>
       <c r="B58" t="n">
-        <v>90006</v>
+        <v>97853</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6972,34 +6972,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7007,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>588287</v>
+        <v>588429</v>
       </c>
       <c r="R58" t="n">
-        <v>6436027</v>
+        <v>6435973</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7037,12 +7034,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7067,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118659974</v>
+        <v>118596728</v>
       </c>
       <c r="B59" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7086,31 +7083,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>588387</v>
+        <v>588287</v>
       </c>
       <c r="R59" t="n">
-        <v>6435972</v>
+        <v>6436027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7148,12 +7148,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7181,7 +7181,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118659945</v>
+        <v>118659974</v>
       </c>
       <c r="B60" t="n">
         <v>97853</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588429</v>
+        <v>588387</v>
       </c>
       <c r="R60" t="n">
-        <v>6435973</v>
+        <v>6435972</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8178,10 +8178,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118660618</v>
+        <v>118659872</v>
       </c>
       <c r="B69" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8190,25 +8190,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8217,11 +8217,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8230,10 +8226,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588407</v>
+        <v>588386</v>
       </c>
       <c r="R69" t="n">
-        <v>6435952</v>
+        <v>6436004</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8293,7 +8289,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118659907</v>
+        <v>118660618</v>
       </c>
       <c r="B70" t="n">
         <v>97853</v>
@@ -8332,7 +8328,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588400</v>
+        <v>588407</v>
       </c>
       <c r="R70" t="n">
-        <v>6435993</v>
+        <v>6435952</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8404,10 +8404,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118659872</v>
+        <v>118659907</v>
       </c>
       <c r="B71" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8416,25 +8416,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588386</v>
+        <v>588400</v>
       </c>
       <c r="R71" t="n">
-        <v>6436004</v>
+        <v>6435993</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118597252</v>
+        <v>118594857</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588324</v>
+        <v>588230</v>
       </c>
       <c r="R2" t="n">
-        <v>6436038</v>
+        <v>6435980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118594699</v>
+        <v>118594955</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588208</v>
+        <v>588225</v>
       </c>
       <c r="R3" t="n">
-        <v>6435965</v>
+        <v>6435968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118597293</v>
+        <v>118596922</v>
       </c>
       <c r="B4" t="n">
-        <v>90915</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588360</v>
+        <v>588264</v>
       </c>
       <c r="R4" t="n">
-        <v>6436048</v>
+        <v>6436046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118596651</v>
+        <v>118597293</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
+        <v>90915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588258</v>
+        <v>588360</v>
       </c>
       <c r="R5" t="n">
-        <v>6435987</v>
+        <v>6436048</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118594857</v>
+        <v>118594658</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588230</v>
+        <v>588211</v>
       </c>
       <c r="R6" t="n">
-        <v>6435980</v>
+        <v>6435962</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118595018</v>
+        <v>118594683</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1272,19 +1272,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588242</v>
+        <v>588206</v>
       </c>
       <c r="R7" t="n">
-        <v>6435991</v>
+        <v>6435960</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118596922</v>
+        <v>118594743</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1392,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588264</v>
+        <v>588239</v>
       </c>
       <c r="R8" t="n">
-        <v>6436046</v>
+        <v>6436002</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118594459</v>
+        <v>118597392</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1503,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588238</v>
+        <v>588372</v>
       </c>
       <c r="R9" t="n">
-        <v>6435934</v>
+        <v>6436011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1570,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118597164</v>
+        <v>118597252</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1614,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588296</v>
+        <v>588324</v>
       </c>
       <c r="R10" t="n">
-        <v>6436035</v>
+        <v>6436038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118597267</v>
+        <v>118594936</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1716,7 +1720,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1725,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588348</v>
+        <v>588234</v>
       </c>
       <c r="R11" t="n">
-        <v>6436039</v>
+        <v>6435965</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118597343</v>
+        <v>118597410</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
+        <v>94627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,33 +1808,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1836,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588368</v>
+        <v>588363</v>
       </c>
       <c r="R12" t="n">
-        <v>6436025</v>
+        <v>6436008</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118594896</v>
+        <v>118594699</v>
       </c>
       <c r="B13" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588223</v>
+        <v>588208</v>
       </c>
       <c r="R13" t="n">
-        <v>6435976</v>
+        <v>6435965</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118594743</v>
+        <v>118597524</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2058,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588239</v>
+        <v>588256</v>
       </c>
       <c r="R14" t="n">
-        <v>6436002</v>
+        <v>6436024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118597219</v>
+        <v>118597598</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,25 +2137,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,7 +2166,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588317</v>
+        <v>588224</v>
       </c>
       <c r="R15" t="n">
-        <v>6436035</v>
+        <v>6435937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118596628</v>
+        <v>118597136</v>
       </c>
       <c r="B16" t="n">
-        <v>97853</v>
+        <v>90915</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,35 +2252,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2284,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588242</v>
+        <v>588295</v>
       </c>
       <c r="R16" t="n">
-        <v>6436014</v>
+        <v>6436061</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118594488</v>
+        <v>118597484</v>
       </c>
       <c r="B17" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,34 +2366,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2395,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588214</v>
+        <v>588339</v>
       </c>
       <c r="R17" t="n">
-        <v>6435937</v>
+        <v>6436034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118594936</v>
+        <v>118594896</v>
       </c>
       <c r="B18" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,25 +2477,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,11 +2504,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2510,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588234</v>
+        <v>588223</v>
       </c>
       <c r="R18" t="n">
-        <v>6435965</v>
+        <v>6435976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118594819</v>
+        <v>118594511</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2612,19 +2615,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27374, Långgölen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588240</v>
+        <v>588220</v>
       </c>
       <c r="R19" t="n">
-        <v>6435993</v>
+        <v>6435969</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118597015</v>
+        <v>118596990</v>
       </c>
       <c r="B20" t="n">
         <v>97853</v>
@@ -2723,7 +2730,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2732,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588316</v>
+        <v>588269</v>
       </c>
       <c r="R20" t="n">
-        <v>6436073</v>
+        <v>6436070</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,7 +2806,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118596899</v>
+        <v>118594794</v>
       </c>
       <c r="B21" t="n">
         <v>97853</v>
@@ -2829,7 +2840,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2843,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588276</v>
+        <v>588252</v>
       </c>
       <c r="R21" t="n">
-        <v>6436025</v>
+        <v>6435994</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118596990</v>
+        <v>118596776</v>
       </c>
       <c r="B22" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,25 +2933,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2945,11 +2960,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2958,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588269</v>
+        <v>588272</v>
       </c>
       <c r="R22" t="n">
-        <v>6436070</v>
+        <v>6436033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3021,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118597598</v>
+        <v>118597458</v>
       </c>
       <c r="B23" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3033,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3060,11 +3071,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3073,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588224</v>
+        <v>588342</v>
       </c>
       <c r="R23" t="n">
-        <v>6435937</v>
+        <v>6436015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3136,7 +3143,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118597469</v>
+        <v>118596899</v>
       </c>
       <c r="B24" t="n">
         <v>97853</v>
@@ -3170,12 +3177,12 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3184,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588317</v>
+        <v>588276</v>
       </c>
       <c r="R24" t="n">
-        <v>6435988</v>
+        <v>6436025</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,7 +3254,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118594834</v>
+        <v>118594721</v>
       </c>
       <c r="B25" t="n">
         <v>97853</v>
@@ -3286,7 +3293,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3295,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588243</v>
+        <v>588225</v>
       </c>
       <c r="R25" t="n">
-        <v>6435983</v>
+        <v>6435977</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3358,7 +3369,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118594446</v>
+        <v>118596857</v>
       </c>
       <c r="B26" t="n">
         <v>97853</v>
@@ -3406,14 +3417,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A  27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588224</v>
+        <v>588255</v>
       </c>
       <c r="R26" t="n">
-        <v>6435907</v>
+        <v>6436028</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3484,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118597392</v>
+        <v>118597118</v>
       </c>
       <c r="B27" t="n">
         <v>97853</v>
@@ -3521,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588372</v>
+        <v>588306</v>
       </c>
       <c r="R27" t="n">
-        <v>6436011</v>
+        <v>6436055</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3584,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118597378</v>
+        <v>118596651</v>
       </c>
       <c r="B28" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3596,25 +3607,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3632,10 +3643,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588349</v>
+        <v>588258</v>
       </c>
       <c r="R28" t="n">
-        <v>6436020</v>
+        <v>6435987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3695,7 +3706,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118594658</v>
+        <v>118597239</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3743,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588211</v>
+        <v>588323</v>
       </c>
       <c r="R29" t="n">
-        <v>6435962</v>
+        <v>6436028</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3806,10 +3817,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118594991</v>
+        <v>118597504</v>
       </c>
       <c r="B30" t="n">
-        <v>97853</v>
+        <v>90915</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3818,39 +3829,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3858,10 +3868,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588220</v>
+        <v>588334</v>
       </c>
       <c r="R30" t="n">
-        <v>6435964</v>
+        <v>6436022</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3921,10 +3931,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118597539</v>
+        <v>118595018</v>
       </c>
       <c r="B31" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3933,25 +3943,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3969,10 +3979,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588236</v>
+        <v>588242</v>
       </c>
       <c r="R31" t="n">
-        <v>6436001</v>
+        <v>6435991</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4032,7 +4042,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118594721</v>
+        <v>118597432</v>
       </c>
       <c r="B32" t="n">
         <v>97853</v>
@@ -4071,11 +4081,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4084,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588225</v>
+        <v>588370</v>
       </c>
       <c r="R32" t="n">
-        <v>6435977</v>
+        <v>6436006</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4147,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118597504</v>
+        <v>118597219</v>
       </c>
       <c r="B33" t="n">
-        <v>90915</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4159,38 +4165,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4198,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588334</v>
+        <v>588317</v>
       </c>
       <c r="R33" t="n">
-        <v>6436022</v>
+        <v>6436035</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4261,10 +4268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118597065</v>
+        <v>118594488</v>
       </c>
       <c r="B34" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4273,35 +4280,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4309,13 +4316,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588304</v>
+        <v>588214</v>
       </c>
       <c r="R34" t="n">
-        <v>6436063</v>
+        <v>6435937</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4347,17 +4354,13 @@
           <t>2024-07-21</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4376,7 +4379,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118594849</v>
+        <v>118597343</v>
       </c>
       <c r="B35" t="n">
         <v>97853</v>
@@ -4415,11 +4418,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4428,10 +4427,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588235</v>
+        <v>588368</v>
       </c>
       <c r="R35" t="n">
-        <v>6435981</v>
+        <v>6436025</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4491,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118597458</v>
+        <v>118596804</v>
       </c>
       <c r="B36" t="n">
         <v>97853</v>
@@ -4530,7 +4529,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4539,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588342</v>
+        <v>588239</v>
       </c>
       <c r="R36" t="n">
-        <v>6436015</v>
+        <v>6436018</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4602,7 +4605,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118597187</v>
+        <v>118594459</v>
       </c>
       <c r="B37" t="n">
         <v>97853</v>
@@ -4650,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588288</v>
+        <v>588238</v>
       </c>
       <c r="R37" t="n">
-        <v>6436050</v>
+        <v>6435934</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4713,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118594734</v>
+        <v>118597378</v>
       </c>
       <c r="B38" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4725,25 +4728,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4757,14 +4760,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588223</v>
+        <v>588349</v>
       </c>
       <c r="R38" t="n">
-        <v>6435976</v>
+        <v>6436020</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4824,10 +4827,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118597484</v>
+        <v>118597561</v>
       </c>
       <c r="B39" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4836,25 +4839,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4863,7 +4866,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4872,10 +4879,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588339</v>
+        <v>588237</v>
       </c>
       <c r="R39" t="n">
-        <v>6436034</v>
+        <v>6435907</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4935,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118597136</v>
+        <v>118597015</v>
       </c>
       <c r="B40" t="n">
-        <v>90915</v>
+        <v>97853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4947,38 +4954,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4986,10 +4990,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588295</v>
+        <v>588316</v>
       </c>
       <c r="R40" t="n">
-        <v>6436061</v>
+        <v>6436073</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5049,7 +5053,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118597239</v>
+        <v>118597164</v>
       </c>
       <c r="B41" t="n">
         <v>97853</v>
@@ -5097,10 +5101,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>588323</v>
+        <v>588296</v>
       </c>
       <c r="R41" t="n">
-        <v>6436028</v>
+        <v>6436035</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5160,7 +5164,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118594794</v>
+        <v>118596628</v>
       </c>
       <c r="B42" t="n">
         <v>97853</v>
@@ -5194,11 +5198,7 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588252</v>
+        <v>588242</v>
       </c>
       <c r="R42" t="n">
-        <v>6435994</v>
+        <v>6436014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118594683</v>
+        <v>118594763</v>
       </c>
       <c r="B43" t="n">
         <v>97853</v>
@@ -5314,23 +5314,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 27374. Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588206</v>
+        <v>588231</v>
       </c>
       <c r="R43" t="n">
-        <v>6435960</v>
+        <v>6435990</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5390,10 +5386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118597574</v>
+        <v>118597539</v>
       </c>
       <c r="B44" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5402,25 +5398,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5438,10 +5434,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>588227</v>
+        <v>588236</v>
       </c>
       <c r="R44" t="n">
-        <v>6435928</v>
+        <v>6436001</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5501,7 +5497,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118594511</v>
+        <v>118597187</v>
       </c>
       <c r="B45" t="n">
         <v>97853</v>
@@ -5540,23 +5536,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 27374, Långgölen, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588220</v>
+        <v>588288</v>
       </c>
       <c r="R45" t="n">
-        <v>6435969</v>
+        <v>6436050</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5616,7 +5608,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118597118</v>
+        <v>118594834</v>
       </c>
       <c r="B46" t="n">
         <v>97853</v>
@@ -5664,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>588306</v>
+        <v>588243</v>
       </c>
       <c r="R46" t="n">
-        <v>6436055</v>
+        <v>6435983</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5727,7 +5719,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118597100</v>
+        <v>118597574</v>
       </c>
       <c r="B47" t="n">
         <v>97853</v>
@@ -5775,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588307</v>
+        <v>588227</v>
       </c>
       <c r="R47" t="n">
-        <v>6436069</v>
+        <v>6435928</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5838,7 +5830,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118596857</v>
+        <v>118594734</v>
       </c>
       <c r="B48" t="n">
         <v>97853</v>
@@ -5877,23 +5869,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>A  27374. Långgöl, Sm</t>
+          <t>A 27374. Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588255</v>
+        <v>588223</v>
       </c>
       <c r="R48" t="n">
-        <v>6436028</v>
+        <v>6435976</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5953,10 +5941,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118597410</v>
+        <v>118594849</v>
       </c>
       <c r="B49" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5965,30 +5953,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5997,10 +5993,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>588363</v>
+        <v>588235</v>
       </c>
       <c r="R49" t="n">
-        <v>6436008</v>
+        <v>6435981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6171,7 +6167,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118597524</v>
+        <v>118594991</v>
       </c>
       <c r="B51" t="n">
         <v>97853</v>
@@ -6210,7 +6206,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588256</v>
+        <v>588220</v>
       </c>
       <c r="R51" t="n">
-        <v>6436024</v>
+        <v>6435964</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6282,10 +6282,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118596776</v>
+        <v>118597100</v>
       </c>
       <c r="B52" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6294,25 +6294,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>588272</v>
+        <v>588307</v>
       </c>
       <c r="R52" t="n">
-        <v>6436033</v>
+        <v>6436069</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6393,10 +6393,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118594955</v>
+        <v>118597065</v>
       </c>
       <c r="B53" t="n">
-        <v>97853</v>
+        <v>57306</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6405,35 +6405,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>588225</v>
+        <v>588304</v>
       </c>
       <c r="R53" t="n">
-        <v>6435968</v>
+        <v>6436063</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6479,13 +6479,17 @@
           <t>2024-07-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På ytterligare 3-4 ställen hittades spår efter spillkråkans födosök.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6504,7 +6508,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118594763</v>
+        <v>118597267</v>
       </c>
       <c r="B54" t="n">
         <v>97853</v>
@@ -6552,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588231</v>
+        <v>588348</v>
       </c>
       <c r="R54" t="n">
-        <v>6435990</v>
+        <v>6436039</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6615,7 +6619,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118597561</v>
+        <v>118597469</v>
       </c>
       <c r="B55" t="n">
         <v>97853</v>
@@ -6654,11 +6658,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588237</v>
+        <v>588317</v>
       </c>
       <c r="R55" t="n">
-        <v>6435907</v>
+        <v>6435988</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118597432</v>
+        <v>118594446</v>
       </c>
       <c r="B56" t="n">
         <v>97853</v>
@@ -6769,7 +6769,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6778,10 +6782,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>588370</v>
+        <v>588224</v>
       </c>
       <c r="R56" t="n">
-        <v>6436006</v>
+        <v>6435907</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6841,7 +6845,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118596804</v>
+        <v>118594819</v>
       </c>
       <c r="B57" t="n">
         <v>97853</v>
@@ -6880,11 +6884,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>588239</v>
+        <v>588240</v>
       </c>
       <c r="R57" t="n">
-        <v>6436018</v>
+        <v>6435993</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118659945</v>
+        <v>118659916</v>
       </c>
       <c r="B58" t="n">
         <v>97853</v>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>588429</v>
+        <v>588419</v>
       </c>
       <c r="R58" t="n">
-        <v>6435973</v>
+        <v>6435978</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7067,10 +7067,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118596728</v>
+        <v>118659907</v>
       </c>
       <c r="B59" t="n">
-        <v>90006</v>
+        <v>97853</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7083,34 +7083,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7118,10 +7115,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>588287</v>
+        <v>588400</v>
       </c>
       <c r="R59" t="n">
-        <v>6436027</v>
+        <v>6435993</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7148,12 +7145,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7181,7 +7178,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118659974</v>
+        <v>118660013</v>
       </c>
       <c r="B60" t="n">
         <v>97853</v>
@@ -7229,10 +7226,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588387</v>
+        <v>588383</v>
       </c>
       <c r="R60" t="n">
-        <v>6435972</v>
+        <v>6435986</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7292,10 +7289,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118660648</v>
+        <v>118659964</v>
       </c>
       <c r="B61" t="n">
-        <v>91786</v>
+        <v>94627</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7308,30 +7305,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7339,10 +7333,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>588400</v>
+        <v>588411</v>
       </c>
       <c r="R61" t="n">
-        <v>6435972</v>
+        <v>6435983</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7402,7 +7396,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118659809</v>
+        <v>118659848</v>
       </c>
       <c r="B62" t="n">
         <v>97853</v>
@@ -7450,10 +7444,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>588355</v>
+        <v>588419</v>
       </c>
       <c r="R62" t="n">
-        <v>6436008</v>
+        <v>6435987</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7513,7 +7507,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118659790</v>
+        <v>118659945</v>
       </c>
       <c r="B63" t="n">
         <v>97853</v>
@@ -7561,10 +7555,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>588326</v>
+        <v>588429</v>
       </c>
       <c r="R63" t="n">
-        <v>6436033</v>
+        <v>6435973</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7624,10 +7618,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118596742</v>
+        <v>118659809</v>
       </c>
       <c r="B64" t="n">
-        <v>90006</v>
+        <v>97853</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7640,34 +7634,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7675,10 +7666,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588295</v>
+        <v>588355</v>
       </c>
       <c r="R64" t="n">
-        <v>6436033</v>
+        <v>6436008</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7705,12 +7696,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7738,10 +7729,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118659964</v>
+        <v>118660618</v>
       </c>
       <c r="B65" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7750,30 +7741,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -7782,10 +7781,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588411</v>
+        <v>588407</v>
       </c>
       <c r="R65" t="n">
-        <v>6435983</v>
+        <v>6435952</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7845,10 +7844,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118660013</v>
+        <v>118596680</v>
       </c>
       <c r="B66" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7861,31 +7860,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7893,10 +7895,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>588383</v>
+        <v>588251</v>
       </c>
       <c r="R66" t="n">
-        <v>6435986</v>
+        <v>6436043</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7923,12 +7925,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7956,10 +7958,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118659916</v>
+        <v>118596728</v>
       </c>
       <c r="B67" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7972,31 +7974,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8004,10 +8009,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>588419</v>
+        <v>588287</v>
       </c>
       <c r="R67" t="n">
-        <v>6435978</v>
+        <v>6436027</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8034,12 +8039,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8067,10 +8072,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118659823</v>
+        <v>118596742</v>
       </c>
       <c r="B68" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8083,31 +8088,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8115,10 +8123,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>588322</v>
+        <v>588295</v>
       </c>
       <c r="R68" t="n">
-        <v>6435984</v>
+        <v>6436033</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8145,12 +8153,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8178,10 +8186,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118659872</v>
+        <v>118659989</v>
       </c>
       <c r="B69" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8190,25 +8198,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8226,10 +8234,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>588386</v>
+        <v>588391</v>
       </c>
       <c r="R69" t="n">
-        <v>6436004</v>
+        <v>6435977</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8289,10 +8297,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118660618</v>
+        <v>118596695</v>
       </c>
       <c r="B70" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8305,35 +8313,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8341,10 +8348,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>588407</v>
+        <v>588270</v>
       </c>
       <c r="R70" t="n">
-        <v>6435952</v>
+        <v>6436044</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8371,12 +8378,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8404,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118659907</v>
+        <v>118596709</v>
       </c>
       <c r="B71" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8420,31 +8427,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8452,10 +8462,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588400</v>
+        <v>588280</v>
       </c>
       <c r="R71" t="n">
-        <v>6435993</v>
+        <v>6436028</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8482,12 +8492,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8515,7 +8525,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118660036</v>
+        <v>118659790</v>
       </c>
       <c r="B72" t="n">
         <v>97853</v>
@@ -8554,11 +8564,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -8567,10 +8573,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>588380</v>
+        <v>588326</v>
       </c>
       <c r="R72" t="n">
-        <v>6435970</v>
+        <v>6436033</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8630,10 +8636,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118596695</v>
+        <v>118660053</v>
       </c>
       <c r="B73" t="n">
-        <v>90006</v>
+        <v>91830</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8642,30 +8648,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2051</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8681,10 +8687,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>588270</v>
+        <v>588406</v>
       </c>
       <c r="R73" t="n">
-        <v>6436044</v>
+        <v>6435986</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8711,12 +8717,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8744,7 +8750,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118659892</v>
+        <v>118659974</v>
       </c>
       <c r="B74" t="n">
         <v>97853</v>
@@ -8792,10 +8798,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>588413</v>
+        <v>588387</v>
       </c>
       <c r="R74" t="n">
-        <v>6435984</v>
+        <v>6435972</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8855,10 +8861,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118596709</v>
+        <v>118659823</v>
       </c>
       <c r="B75" t="n">
-        <v>90006</v>
+        <v>97853</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8871,34 +8877,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8906,10 +8909,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>588280</v>
+        <v>588322</v>
       </c>
       <c r="R75" t="n">
-        <v>6436028</v>
+        <v>6435984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8936,12 +8939,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8969,7 +8972,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118659848</v>
+        <v>118660036</v>
       </c>
       <c r="B76" t="n">
         <v>97853</v>
@@ -9008,7 +9011,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -9017,10 +9024,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>588419</v>
+        <v>588380</v>
       </c>
       <c r="R76" t="n">
-        <v>6435987</v>
+        <v>6435970</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9080,10 +9087,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118660053</v>
+        <v>118659892</v>
       </c>
       <c r="B77" t="n">
-        <v>91830</v>
+        <v>97853</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9092,38 +9099,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9131,10 +9135,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>588406</v>
+        <v>588413</v>
       </c>
       <c r="R77" t="n">
-        <v>6435986</v>
+        <v>6435984</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9194,10 +9198,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118659989</v>
+        <v>118660648</v>
       </c>
       <c r="B78" t="n">
-        <v>97853</v>
+        <v>91786</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9206,35 +9210,34 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9242,10 +9245,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588391</v>
+        <v>588400</v>
       </c>
       <c r="R78" t="n">
-        <v>6435977</v>
+        <v>6435972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9305,10 +9308,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118596680</v>
+        <v>118659872</v>
       </c>
       <c r="B79" t="n">
-        <v>90006</v>
+        <v>104947</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9317,38 +9320,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2051</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>588251</v>
+        <v>588386</v>
       </c>
       <c r="R79" t="n">
-        <v>6436043</v>
+        <v>6436004</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9386,12 +9386,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -10561,7 +10561,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119750095</v>
+        <v>119749338</v>
       </c>
       <c r="B90" t="n">
         <v>91840</v>
@@ -10608,14 +10608,14 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>588401</v>
+        <v>588389</v>
       </c>
       <c r="R90" t="n">
-        <v>6435999</v>
+        <v>6435981</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10675,7 +10675,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119749338</v>
+        <v>119750095</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10722,14 +10722,14 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>588389</v>
+        <v>588401</v>
       </c>
       <c r="R91" t="n">
-        <v>6435981</v>
+        <v>6435999</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -9877,10 +9877,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119749175</v>
+        <v>119750095</v>
       </c>
       <c r="B84" t="n">
-        <v>90966</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9924,14 +9924,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>588343</v>
+        <v>588401</v>
       </c>
       <c r="R84" t="n">
-        <v>6436050</v>
+        <v>6435999</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119749263</v>
+        <v>119750175</v>
       </c>
       <c r="B87" t="n">
         <v>91840</v>
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>588372</v>
+        <v>588349</v>
       </c>
       <c r="R87" t="n">
-        <v>6436012</v>
+        <v>6436006</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119750117</v>
+        <v>119749263</v>
       </c>
       <c r="B88" t="n">
         <v>91840</v>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>588381</v>
+        <v>588372</v>
       </c>
       <c r="R88" t="n">
         <v>6436012</v>
@@ -10447,7 +10447,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119749196</v>
+        <v>119750117</v>
       </c>
       <c r="B89" t="n">
         <v>91840</v>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>588215</v>
+        <v>588381</v>
       </c>
       <c r="R89" t="n">
-        <v>6435970</v>
+        <v>6436012</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10561,10 +10561,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119749338</v>
+        <v>119749175</v>
       </c>
       <c r="B90" t="n">
-        <v>91840</v>
+        <v>90966</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10577,21 +10577,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>588389</v>
+        <v>588343</v>
       </c>
       <c r="R90" t="n">
-        <v>6435981</v>
+        <v>6436050</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10675,7 +10675,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119750095</v>
+        <v>119749196</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10710,26 +10710,26 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>588401</v>
+        <v>588215</v>
       </c>
       <c r="R91" t="n">
-        <v>6435999</v>
+        <v>6435970</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10789,7 +10789,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119750175</v>
+        <v>119749338</v>
       </c>
       <c r="B92" t="n">
         <v>91840</v>
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>588349</v>
+        <v>588389</v>
       </c>
       <c r="R92" t="n">
-        <v>6436006</v>
+        <v>6435981</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -9877,7 +9877,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119750095</v>
+        <v>119749263</v>
       </c>
       <c r="B84" t="n">
         <v>91840</v>
@@ -9924,14 +9924,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>588401</v>
+        <v>588372</v>
       </c>
       <c r="R84" t="n">
-        <v>6435999</v>
+        <v>6436012</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119749292</v>
+        <v>119749175</v>
       </c>
       <c r="B85" t="n">
-        <v>91836</v>
+        <v>90966</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10007,21 +10007,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4363</v>
+        <v>5420</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>588374</v>
+        <v>588343</v>
       </c>
       <c r="R85" t="n">
-        <v>6436007</v>
+        <v>6436050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10105,7 +10105,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119749117</v>
+        <v>119749196</v>
       </c>
       <c r="B86" t="n">
         <v>91840</v>
@@ -10156,10 +10156,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>588221</v>
+        <v>588215</v>
       </c>
       <c r="R86" t="n">
-        <v>6435885</v>
+        <v>6435970</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10212,14 +10212,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119750175</v>
+        <v>119749117</v>
       </c>
       <c r="B87" t="n">
         <v>91840</v>
@@ -10254,12 +10254,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>588349</v>
+        <v>588221</v>
       </c>
       <c r="R87" t="n">
-        <v>6436006</v>
+        <v>6435885</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10326,17 +10326,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119749263</v>
+        <v>119749292</v>
       </c>
       <c r="B88" t="n">
-        <v>91840</v>
+        <v>91836</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10349,21 +10349,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>588372</v>
+        <v>588374</v>
       </c>
       <c r="R88" t="n">
-        <v>6436012</v>
+        <v>6436007</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10447,7 +10447,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119750117</v>
+        <v>119750175</v>
       </c>
       <c r="B89" t="n">
         <v>91840</v>
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>588381</v>
+        <v>588349</v>
       </c>
       <c r="R89" t="n">
-        <v>6436012</v>
+        <v>6436006</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10561,10 +10561,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119749175</v>
+        <v>119749338</v>
       </c>
       <c r="B90" t="n">
-        <v>90966</v>
+        <v>91840</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10577,21 +10577,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>588343</v>
+        <v>588389</v>
       </c>
       <c r="R90" t="n">
-        <v>6436050</v>
+        <v>6435981</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10675,7 +10675,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119749196</v>
+        <v>119750117</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>588215</v>
+        <v>588381</v>
       </c>
       <c r="R91" t="n">
-        <v>6435970</v>
+        <v>6436012</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10789,7 +10789,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119749338</v>
+        <v>119750095</v>
       </c>
       <c r="B92" t="n">
         <v>91840</v>
@@ -10836,14 +10836,14 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>588389</v>
+        <v>588401</v>
       </c>
       <c r="R92" t="n">
-        <v>6435981</v>
+        <v>6435999</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -9877,7 +9877,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119749263</v>
+        <v>119750117</v>
       </c>
       <c r="B84" t="n">
         <v>91840</v>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>588372</v>
+        <v>588381</v>
       </c>
       <c r="R84" t="n">
         <v>6436012</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119749175</v>
+        <v>119749263</v>
       </c>
       <c r="B85" t="n">
-        <v>90966</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10007,21 +10007,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>588343</v>
+        <v>588372</v>
       </c>
       <c r="R85" t="n">
-        <v>6436050</v>
+        <v>6436012</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10105,7 +10105,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119749196</v>
+        <v>119749338</v>
       </c>
       <c r="B86" t="n">
         <v>91840</v>
@@ -10140,12 +10140,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -10156,10 +10156,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>588215</v>
+        <v>588389</v>
       </c>
       <c r="R86" t="n">
-        <v>6435970</v>
+        <v>6435981</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10219,10 +10219,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119749117</v>
+        <v>119749175</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>90966</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10235,31 +10235,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>588221</v>
+        <v>588343</v>
       </c>
       <c r="R87" t="n">
-        <v>6435885</v>
+        <v>6436050</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10326,17 +10326,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119749292</v>
+        <v>119750095</v>
       </c>
       <c r="B88" t="n">
-        <v>91836</v>
+        <v>91840</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10349,21 +10349,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10380,14 +10380,14 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>588374</v>
+        <v>588401</v>
       </c>
       <c r="R88" t="n">
-        <v>6436007</v>
+        <v>6435999</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10447,10 +10447,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119750175</v>
+        <v>119749292</v>
       </c>
       <c r="B89" t="n">
-        <v>91840</v>
+        <v>91836</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>588349</v>
+        <v>588374</v>
       </c>
       <c r="R89" t="n">
-        <v>6436006</v>
+        <v>6436007</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10561,7 +10561,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119749338</v>
+        <v>119749196</v>
       </c>
       <c r="B90" t="n">
         <v>91840</v>
@@ -10596,12 +10596,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>588389</v>
+        <v>588215</v>
       </c>
       <c r="R90" t="n">
-        <v>6435981</v>
+        <v>6435970</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10675,7 +10675,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119750117</v>
+        <v>119749117</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>588381</v>
+        <v>588221</v>
       </c>
       <c r="R91" t="n">
-        <v>6436012</v>
+        <v>6435885</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10782,14 +10782,14 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119750095</v>
+        <v>119750175</v>
       </c>
       <c r="B92" t="n">
         <v>91840</v>
@@ -10836,14 +10836,14 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>588401</v>
+        <v>588349</v>
       </c>
       <c r="R92" t="n">
-        <v>6435999</v>
+        <v>6436006</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 27374-2024 artfynd.xlsx
+++ b/artfynd/A 27374-2024 artfynd.xlsx
@@ -9877,10 +9877,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119750117</v>
+        <v>119749292</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>91854</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>588381</v>
+        <v>588374</v>
       </c>
       <c r="R84" t="n">
-        <v>6436012</v>
+        <v>6436007</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119749263</v>
+        <v>119750175</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>588372</v>
+        <v>588349</v>
       </c>
       <c r="R85" t="n">
-        <v>6436012</v>
+        <v>6436006</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10105,10 +10105,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119749338</v>
+        <v>119749196</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10140,12 +10140,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -10156,10 +10156,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>588389</v>
+        <v>588215</v>
       </c>
       <c r="R86" t="n">
-        <v>6435981</v>
+        <v>6435970</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10222,7 +10222,7 @@
         <v>119749175</v>
       </c>
       <c r="B87" t="n">
-        <v>90966</v>
+        <v>90984</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10333,10 +10333,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119750095</v>
+        <v>119750117</v>
       </c>
       <c r="B88" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10380,14 +10380,14 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27374, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>588401</v>
+        <v>588381</v>
       </c>
       <c r="R88" t="n">
-        <v>6435999</v>
+        <v>6436012</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10447,10 +10447,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119749292</v>
+        <v>119749263</v>
       </c>
       <c r="B89" t="n">
-        <v>91836</v>
+        <v>91858</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10463,21 +10463,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>588374</v>
+        <v>588372</v>
       </c>
       <c r="R89" t="n">
-        <v>6436007</v>
+        <v>6436012</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10561,10 +10561,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119749196</v>
+        <v>119749338</v>
       </c>
       <c r="B90" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10596,12 +10596,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>588215</v>
+        <v>588389</v>
       </c>
       <c r="R90" t="n">
-        <v>6435970</v>
+        <v>6435981</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10678,7 +10678,7 @@
         <v>119749117</v>
       </c>
       <c r="B91" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10789,10 +10789,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119750175</v>
+        <v>119750095</v>
       </c>
       <c r="B92" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10836,14 +10836,14 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>A 27374, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>588349</v>
+        <v>588401</v>
       </c>
       <c r="R92" t="n">
-        <v>6436006</v>
+        <v>6435999</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
